--- a/AAII_Financials/Quarterly/DG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>DG</t>
   </si>
@@ -656,383 +656,395 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45233</v>
+      </c>
+      <c r="E7" s="2">
         <v>45142</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45051</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44960</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44862</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44771</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44680</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44589</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44498</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44407</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44225</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44134</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43952</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43861</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43770</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43679</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43588</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43497</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43406</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43315</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43224</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43133</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43042</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42951</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42860</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42769</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9694100</v>
+      </c>
+      <c r="E8" s="3">
         <v>9796200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9342800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10202900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9464900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9425700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8751400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8651400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8517800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8650200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8401000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8414500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8199600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8684200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8448400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7157600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6991400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6981800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>6623200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6649800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6417500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6443300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6114500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6129400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5903600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5828300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5609600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6009200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5320000</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6881600</v>
+      </c>
+      <c r="E9" s="3">
         <v>6751500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6387400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7054600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6579700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6377500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6013000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5951200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5898400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5912500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5645300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5677800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5631400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5866000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5852800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4884900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4926300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4832800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4620900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4578100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4522400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4468400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4252200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4164000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4137200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4037800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3910600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4108500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3732500</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2812500</v>
+      </c>
+      <c r="E10" s="3">
         <v>3044700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2955400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3148300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2885200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3048200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2738400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2700200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2619400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2737700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2755700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2736700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2568200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2818200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2595600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2272700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2065100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2149000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2002300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2071700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1895100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1974900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1862300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1965400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1766500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1790500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1699000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1900700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1587500</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1064,8 +1076,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,8 +1166,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1242,8 +1258,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1277,8 +1296,8 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1289,17 +1308,17 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>31000</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
@@ -1313,8 +1332,8 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1322,8 +1341,8 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
@@ -1331,8 +1350,11 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1420,8 +1442,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1450,186 +1475,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9260600</v>
+      </c>
+      <c r="E17" s="3">
         <v>9103900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8602000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9269700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8729300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8512300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8005200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7854800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7852300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7800600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7492100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7542300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7426500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7641600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7581700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6436800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6500000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6404000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6110900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6011300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5975300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5897800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5624300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5506000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5486200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5335200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5135800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5328600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4927000</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>433500</v>
+      </c>
+      <c r="E18" s="3">
         <v>692300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>740800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>933200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>735600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>913400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>746200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>796600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>665500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>849600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>908900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>872200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>773100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1042600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>866700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>720800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>491400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>577800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>512300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>638500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>442200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>545500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>490200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>623400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>417400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>493100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>473800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>680600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>393000</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1661,8 +1693,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1676,11 +1709,11 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-400</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
@@ -1727,11 +1760,11 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
@@ -1742,372 +1775,387 @@
         <v>0</v>
       </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>649000</v>
+      </c>
+      <c r="E21" s="3">
         <v>900700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>942800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1125500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>917900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1090600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>918700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>963000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>827900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1008100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1063000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1022000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>919000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1183600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1004400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>853300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>617900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>701200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>634700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>756300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>557000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>656600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>599500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>729100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>518400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>592200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>568900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>778200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>488400</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>82300</v>
+      </c>
+      <c r="E22" s="3">
         <v>84300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>83000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>74800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>53700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>43100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>39700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>38500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>39200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>39400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>40400</v>
-      </c>
-      <c r="N22" s="3">
-        <v>40300</v>
       </c>
       <c r="O22" s="3">
         <v>40300</v>
       </c>
       <c r="P22" s="3">
+        <v>40300</v>
+      </c>
+      <c r="Q22" s="3">
         <v>39300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>30500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>25600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>24300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>24800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>25900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>25100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>24600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>25500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>24800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>24300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>24000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>23700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>25000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>25500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>351200</v>
+      </c>
+      <c r="E23" s="3">
         <v>608000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>657800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>858400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>681400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>870300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>706500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>758200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>626400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>810100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>868500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>832000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>732800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1003300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>836300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>695300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>467200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>553000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>486300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>613400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>417600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>519000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>465400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>599200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>393400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>469400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>445300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>655100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>369100</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>74900</v>
+      </c>
+      <c r="E24" s="3">
         <v>139100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>143400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>199200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>155300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>192300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>153800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>160700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>139400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>173100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>190700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>189200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>158600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>215700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>185800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>159900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>101600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>126400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>101300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>142400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>83400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>111800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>100600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>197800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>140900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>174600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>165800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>240900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2195,186 +2243,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>276200</v>
+      </c>
+      <c r="E26" s="3">
         <v>468800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>514400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>659100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>526200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>678000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>552700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>597400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>487000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>637000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>677700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>642700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>574300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>787600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>650400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>535400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>365600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>426600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>385000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>471000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>334100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>407200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>364900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>401400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>252500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>294800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>279500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>414200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>276200</v>
+      </c>
+      <c r="E27" s="3">
         <v>468800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>514400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>659100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>526200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>678000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>552700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>597400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>487000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>637000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>677700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>642700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>574300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>787600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>650400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>535400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>365600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>426600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>385000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>471000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>334100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>407200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>364900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>401400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>252500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>294800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>279500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>414200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2462,8 +2519,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2500,8 +2560,8 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>8</v>
@@ -2509,11 +2569,11 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3" t="s">
+      <c r="R29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2521,11 +2581,11 @@
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W29" s="3">
         <v>12200</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2533,11 +2593,11 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>310800</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2551,8 +2611,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2640,8 +2703,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2729,8 +2795,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2744,11 +2813,11 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>400</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
@@ -2795,11 +2864,11 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>1000</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
@@ -2810,105 +2879,111 @@
         <v>0</v>
       </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>3500</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>276200</v>
+      </c>
+      <c r="E33" s="3">
         <v>468800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>514400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>659100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>526200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>678000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>552700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>597400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>487000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>637000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>677700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>642700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>574300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>787600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>650400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>535400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>365600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>426600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>385000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>483200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>334100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>407200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>364900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>712200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>252500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>294800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>279500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>414200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2996,191 +3071,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>276200</v>
+      </c>
+      <c r="E35" s="3">
         <v>468800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>514400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>659100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>526200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>678000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>552700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>597400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>487000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>637000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>677700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>642700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>574300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>787600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>650400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>535400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>365600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>426600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>385000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>483200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>334100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>407200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>364900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>712200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>252500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>294800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>279500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>414200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45233</v>
+      </c>
+      <c r="E38" s="2">
         <v>45142</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45051</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44960</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44862</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44771</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44680</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44589</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44498</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44407</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44225</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44134</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43952</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43861</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43770</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43679</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43588</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43497</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43406</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43315</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43224</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43133</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43042</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42951</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42860</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42769</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3212,8 +3296,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3245,97 +3330,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>365400</v>
+      </c>
+      <c r="E41" s="3">
         <v>353000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>313100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>381600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>362700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>326300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>335600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>344800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>488700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>313700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>688100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1376600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2199400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2959600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2673900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>240300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>276100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>259600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>271100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>235500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>260700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>265300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>284000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>267400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>226200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>214200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>206000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>187900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>200200</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3423,364 +3512,379 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>197600</v>
+      </c>
+      <c r="E43" s="3">
         <v>151700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>50900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>135800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>188100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>93300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>33600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>97400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>120400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>127000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>16600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>90800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>111100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>36200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>17200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>76500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>103200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>61700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>25200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>57800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>114600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>68400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>28600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>108300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>99700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>44300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>10500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>11100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>54600</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7356100</v>
+      </c>
+      <c r="E44" s="3">
         <v>7531500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7335800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6760700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7144700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6935900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6087400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5614300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5298900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5279300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5099500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5247500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5025800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4391200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4107300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4676800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4496400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4419600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4109800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4097000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3979100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3896400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3594500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3609000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3597200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3463000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3300100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3258800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3488200</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>352000</v>
+      </c>
+      <c r="E45" s="3">
         <v>377800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>355700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>302900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>321500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>327500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>280300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>247300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>273900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>272800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>237600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>199400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>197000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>210500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>194000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>184200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>192900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>178300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>177700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>272700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>275900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>287800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>258900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>263100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>230300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>258600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>232400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>220000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>225400</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8271100</v>
+      </c>
+      <c r="E46" s="3">
         <v>8414000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8055500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7581000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8017000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7682900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6736900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6303800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6181800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5992700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6041700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6914200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7533400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7597400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6992500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5177900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5068500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4919100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4583800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4663000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4630300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4517800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4166000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4247900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4153300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3980000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3748900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3677800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3968500</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3868,97 +3972,103 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16752700</v>
+      </c>
+      <c r="E48" s="3">
         <v>16379300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>16146700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15906300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>15396800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14967400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>14634200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14439100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14160500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13909300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13614100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13373300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13045200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12675800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12280900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12074500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11770500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11425800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11148800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2970800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2921900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2857300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2758400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2701300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2654900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2574800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2487300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2434500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2388500</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3984,7 +4094,7 @@
         <v>5538300</v>
       </c>
       <c r="K49" s="3">
-        <v>5538400</v>
+        <v>5538300</v>
       </c>
       <c r="L49" s="3">
         <v>5538400</v>
@@ -3993,7 +4103,7 @@
         <v>5538400</v>
       </c>
       <c r="N49" s="3">
-        <v>5538500</v>
+        <v>5538400</v>
       </c>
       <c r="O49" s="3">
         <v>5538500</v>
@@ -4002,7 +4112,7 @@
         <v>5538500</v>
       </c>
       <c r="Q49" s="3">
-        <v>5538600</v>
+        <v>5538500</v>
       </c>
       <c r="R49" s="3">
         <v>5538600</v>
@@ -4011,43 +4121,46 @@
         <v>5538600</v>
       </c>
       <c r="T49" s="3">
+        <v>5538600</v>
+      </c>
+      <c r="U49" s="3">
         <v>5538700</v>
-      </c>
-      <c r="U49" s="3">
-        <v>5538800</v>
       </c>
       <c r="V49" s="3">
         <v>5538800</v>
       </c>
       <c r="W49" s="3">
-        <v>5538900</v>
+        <v>5538800</v>
       </c>
       <c r="X49" s="3">
         <v>5538900</v>
       </c>
       <c r="Y49" s="3">
-        <v>5539000</v>
+        <v>5538900</v>
       </c>
       <c r="Z49" s="3">
         <v>5539000</v>
       </c>
       <c r="AA49" s="3">
-        <v>5539100</v>
+        <v>5539000</v>
       </c>
       <c r="AB49" s="3">
         <v>5539100</v>
       </c>
       <c r="AC49" s="3">
-        <v>5539200</v>
+        <v>5539100</v>
       </c>
       <c r="AD49" s="3">
         <v>5539200</v>
       </c>
       <c r="AE49" s="3">
+        <v>5539200</v>
+      </c>
+      <c r="AF49" s="3">
         <v>5539300</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4135,8 +4248,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4224,70 +4340,73 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>62600</v>
+      </c>
+      <c r="E52" s="3">
         <v>64000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>63500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>57700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>55000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>50700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>46900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>46100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>44600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>47400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>42400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>36600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>36400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>35700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>36300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>34100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>35100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>33900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>33000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>31400</v>
-      </c>
-      <c r="W52" s="3">
-        <v>29900</v>
       </c>
       <c r="X52" s="3">
         <v>29900</v>
@@ -4296,25 +4415,28 @@
         <v>29900</v>
       </c>
       <c r="Z52" s="3">
+        <v>29900</v>
+      </c>
+      <c r="AA52" s="3">
         <v>28800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>27400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>26900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>20900</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>20800</v>
       </c>
       <c r="AE52" s="3">
         <v>20800</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>20800</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4402,97 +4524,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30624600</v>
+      </c>
+      <c r="E54" s="3">
         <v>30395600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>29803900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>29083400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>29007200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>28239300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>26956300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>26327400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>25925300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>25487800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>25236700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>25862600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>26153400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>25847400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>24848300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>22825100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>22412800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>21917500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>21304300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>13204000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>13121000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>12943900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>12493200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>12516900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12374800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12120800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>11796400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>11672300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>11917100</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4524,8 +4652,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4557,120 +4686,124 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3651800</v>
+      </c>
+      <c r="E57" s="3">
         <v>3681600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3679200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3553000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4127100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4358400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3906900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3738600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3532600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3370000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3294400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3614100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3770500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3400600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2954400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2860700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2844200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2727100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2452900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2385500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2336800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2295000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2018300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2009800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1978000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1880700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1622800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1557600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1948100</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D58" s="3">
+        <v>750000</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>250000</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H58" s="3">
-        <v>900600</v>
+      <c r="H58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I58" s="3">
         <v>900600</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>8</v>
+      <c r="J58" s="3">
+        <v>900600</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>8</v>
@@ -4690,8 +4823,8 @@
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q58" s="3">
-        <v>600</v>
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R58" s="3">
         <v>600</v>
@@ -4706,10 +4839,10 @@
         <v>600</v>
       </c>
       <c r="V58" s="3">
+        <v>600</v>
+      </c>
+      <c r="W58" s="3">
         <v>2000</v>
-      </c>
-      <c r="W58" s="3">
-        <v>1900</v>
       </c>
       <c r="X58" s="3">
         <v>1900</v>
@@ -4718,381 +4851,396 @@
         <v>1900</v>
       </c>
       <c r="Z58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AA58" s="3">
         <v>401300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>401500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>401400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>401200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>501000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>501500</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2385300</v>
+      </c>
+      <c r="E59" s="3">
         <v>2352300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2171500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2334800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2375600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2307800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2144400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2240800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2207900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2109100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2021000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2096700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2115700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2010500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1888300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1682300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1661300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1584600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1503300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>628400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>643500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>618600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>505100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>553800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>558200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>524700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>668100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>564300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>510100</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6787100</v>
+      </c>
+      <c r="E60" s="3">
         <v>6033900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6100700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5887800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6502600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7566800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6951800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5979400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5740500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5479100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5315400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5710800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5886200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5411200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4843200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4543000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4506000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4312300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3956700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3015900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2982200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2915500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2525300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2964900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2937800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2806800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2692000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2622800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2959700</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6440800</v>
+      </c>
+      <c r="E61" s="3">
         <v>7295200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7028800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7009400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5985700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4290700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3947500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4172100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4127400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4156800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4130700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4131000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4131600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4089000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3967200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2912000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2762500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2573500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2732100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2862700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2902400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2776800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2862500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2604600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2719600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2683100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2632100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2710600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2673200</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10944800</v>
+      </c>
+      <c r="E62" s="3">
         <v>10768700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10739200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10644400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10425000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10193300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10095400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9914000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9867600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9714800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9540700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9359600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9150100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8991200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8828400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>8667600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8496000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8282600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8042800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>908000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>880500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>872700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>869100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>821600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>973200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>943900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>943300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>932600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>922300</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5180,8 +5328,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5269,8 +5420,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5358,97 +5512,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24172700</v>
+      </c>
+      <c r="E66" s="3">
         <v>24097900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>23868700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>23541600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>22913400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>22050800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>20994700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>20065400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>19735500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>19350700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18986800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>19201400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19167900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18491400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>17638900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>16122600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15764500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15168400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14731600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6786600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6765100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6565000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6256900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6391100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6630600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6433700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6267500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6266000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6555200</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5480,8 +5640,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5569,8 +5730,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5658,8 +5822,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5747,8 +5914,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5836,97 +6006,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2527200</v>
+      </c>
+      <c r="E72" s="3">
         <v>2380500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2041100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1656100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2222800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2364100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2157600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2474000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2461200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2429800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2588000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3006100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3346800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3759000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3659800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3162700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3120700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3234900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3074600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2941100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2890100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2928100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2795600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2698400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2334500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2286100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2136400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2015900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1978000</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6014,8 +6190,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6103,8 +6282,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6192,97 +6374,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6451900</v>
+      </c>
+      <c r="E76" s="3">
         <v>6297700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5935300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5541800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6093800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6188500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5961600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6262000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6189800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6137100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6249900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6661200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6985500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7356100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7209500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6702500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6648300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6749200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6572700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6417400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6355900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6378900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6236300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6125800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5744200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5687100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>5528900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5406300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5361900</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6370,191 +6558,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45233</v>
+      </c>
+      <c r="E80" s="2">
         <v>45142</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45051</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44960</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44862</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44771</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44680</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44589</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44498</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44407</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44225</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44134</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43952</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43861</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43770</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43679</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43588</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43497</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43406</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43315</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43224</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43133</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43042</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42951</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42860</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42769</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>276200</v>
+      </c>
+      <c r="E81" s="3">
         <v>468800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>514400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>659100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>526200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>678000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>552700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>597400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>487000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>637000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>677700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>642700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>574300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>787600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>650400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>535400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>365600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>426600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>385000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>483200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>334100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>407200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>364900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>712200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>252500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>294800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>279500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>414200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6586,97 +6783,101 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>215500</v>
+      </c>
+      <c r="E83" s="3">
         <v>208400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>201900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>192400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>182800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>177200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>172600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>166400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>162300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>158500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>154100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>149800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>145800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>141000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>137700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>132400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>126500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>123400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>122500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>117800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>114900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>112200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>109300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>105700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>101000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>99000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>98600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>97500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>95400</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6764,8 +6965,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6853,8 +7057,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6942,8 +7149,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7031,8 +7241,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7120,97 +7333,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>715300</v>
+      </c>
+      <c r="E89" s="3">
         <v>535600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>191100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>736400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>300200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>498500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>449500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>639100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>909200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>614600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>703000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>492600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>476200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1171000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1736300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>576900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>530600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>556300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>574200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>629400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>416800</v>
-      </c>
-      <c r="X89" s="3">
-        <v>548600</v>
       </c>
       <c r="Y89" s="3">
         <v>548600</v>
       </c>
       <c r="Z89" s="3">
+        <v>548600</v>
+      </c>
+      <c r="AA89" s="3">
         <v>659200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>356700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>275800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>510500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>480600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>331100</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7242,97 +7461,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-472600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-404800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-363100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-482400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-419400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-377200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-281600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-291100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-260900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-240700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-277700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-330400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-273400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-228700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-195400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-266800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-225000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-148300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-144800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-183500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-179900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-206300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-164600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-157800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-174600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-170500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-143500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-154400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-138100</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7420,8 +7643,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7509,97 +7735,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-470800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-403100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-361600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-479500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-419200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-375800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-280800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-290100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-258800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-239700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-276900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-328900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-272900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-228100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-195000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-266300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-224500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-147300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-144300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-182500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-179500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-205600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-164000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-157400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-173900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-170300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-143400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-149400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-136200</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7631,8 +7863,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7640,88 +7873,91 @@
         <v>-129500</v>
       </c>
       <c r="E96" s="3">
+        <v>-129500</v>
+      </c>
+      <c r="F96" s="3">
         <v>-129400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-121300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-123000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-124200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-125300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-96800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-97300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-98300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-99800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-87300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-88400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-89700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-90600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-80800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-81600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-82400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-82800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-75300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>118300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-271900</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-77700</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-70000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-70600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-71000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-71300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-68900</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-70100</v>
       </c>
     </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7809,8 +8045,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7898,8 +8137,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7987,97 +8229,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-232000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-92600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>102000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-238000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>155500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-132100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-177900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-492800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-475400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-749200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1114600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-986600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-963500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-657200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>892200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-346300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-289500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-420600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-394300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-472100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-242000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-361700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-368100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-460600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-170700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-97300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-349000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-343600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-179700</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8165,93 +8413,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E102" s="3">
         <v>40000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-68500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>18800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>36500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-143800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>175000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-374400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-688500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-822900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-760200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>285700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2433600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-35800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>16500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-11500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>35600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-25200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-18700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>16500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>41200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>12000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>8200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>18100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-12300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>15200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
   <si>
     <t>DG</t>
   </si>
@@ -656,395 +656,419 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45415</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45324</v>
+      </c>
+      <c r="F7" s="2">
         <v>45233</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45142</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45051</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44960</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44862</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44771</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44680</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44589</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44498</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44407</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44316</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44225</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44134</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44043</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43952</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43861</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43770</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43679</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43588</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43497</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43406</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43315</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43224</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43133</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43042</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42951</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42860</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42769</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9914000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>9858500</v>
+      </c>
+      <c r="F8" s="3">
         <v>9694100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>9796200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>9342800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>10202900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>9464900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>9425700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>8751400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>8651400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>8517800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>8650200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>8401000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>8414500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>8199600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>8684200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>8448400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>7157600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>6991400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>6981800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>6623200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>6649800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>6417500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>6443300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>6114500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>6129400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>5903600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>5828300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>5609600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>6009200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>5320000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6921900</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6952200</v>
+      </c>
+      <c r="F9" s="3">
         <v>6881600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>6751500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>6387400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>7054600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>6579700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>6377500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>6013000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>5951200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>5898400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>5912500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>5645300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>5677800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>5631400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>5866000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>5852800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>4884900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>4926300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>4832800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>4620900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>4578100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>4522400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>4468400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>4252200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>4164000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>4137200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>4037800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>3910600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>4108500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>3732500</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2992100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2906300</v>
+      </c>
+      <c r="F10" s="3">
         <v>2812500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>3044700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>2955400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>3148300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>2885200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>3048200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2738400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>2700200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>2619400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>2737700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>2755700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>2736700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>2568200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>2818200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>2595600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>2272700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>2065100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>2149000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>2002300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>2071700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1895100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>1974900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1862300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>1965400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>1766500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>1790500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>1699000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>1900700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>1587500</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1077,8 +1101,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1169,8 +1195,14 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1261,8 +1293,14 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1299,11 +1337,11 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
@@ -1311,20 +1349,20 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>31000</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
@@ -1335,26 +1373,32 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1445,8 +1489,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1476,192 +1526,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9367900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>9278900</v>
+      </c>
+      <c r="F17" s="3">
         <v>9260600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>9103900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>8602000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>9269700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>8729300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>8512300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>8005200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>7854800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>7852300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>7800600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>7492100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>7542300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>7426500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>7641600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>7581700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>6436800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>6500000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>6404000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>6110900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>6011300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>5975300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>5897800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>5624300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>5506000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>5486200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>5335200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>5135800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>5328600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>4927000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>546100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>579600</v>
+      </c>
+      <c r="F18" s="3">
         <v>433500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>692300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>740800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>933200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>735600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>913400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>746200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>796600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>665500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>849600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>908900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>872200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>773100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>1042600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>866700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>720800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>491400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>577800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>512300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>638500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>442200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>545500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>490200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>623400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>417400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>493100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>473800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>680600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>393000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1694,8 +1758,10 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1712,14 +1778,14 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-400</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
@@ -1763,14 +1829,14 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
@@ -1778,384 +1844,414 @@
         <v>0</v>
       </c>
       <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>778400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>802600</v>
+      </c>
+      <c r="F21" s="3">
         <v>649000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>900700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>942800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>1125500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>917900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>1090600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>918700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>963000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>827900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1008100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1063000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1022000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>919000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1183600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1004400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>853300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>617900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>701200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>634700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>756300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>557000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>656600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>599500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>729100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>518400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>592200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>568900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>778200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>488400</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>72400</v>
+      </c>
+      <c r="E22" s="3">
+        <v>77100</v>
+      </c>
+      <c r="F22" s="3">
         <v>82300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>84300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>83000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>74800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>53700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>43100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>39700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>38500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>39200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>39400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>40400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>40300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>40300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>39300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>30500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>25600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>24300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>24800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>25900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>25100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>24600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>25500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>24800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>24300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>24000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>23700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>25000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>25500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>473700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>502500</v>
+      </c>
+      <c r="F23" s="3">
         <v>351200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>608000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>657800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>858400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>681400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>870300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>706500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>758200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>626400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>810100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>868500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>832000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>732800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1003300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>836300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>695300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>467200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>553000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>486300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>613400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>417600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>519000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>465400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>599200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>393400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>469400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>445300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>655100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>369100</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>110400</v>
+      </c>
+      <c r="E24" s="3">
+        <v>100700</v>
+      </c>
+      <c r="F24" s="3">
         <v>74900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>139100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>143400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>199200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>155300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>192300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>153800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>160700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>139400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>173100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>190700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>189200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>158600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>215700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>185800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>159900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>101600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>126400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>101300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>142400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>83400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>111800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>100600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>197800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>140900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>174600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>165800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>240900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2246,192 +2342,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>363300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>401800</v>
+      </c>
+      <c r="F26" s="3">
         <v>276200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>468800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>514400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>659100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>526200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>678000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>552700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>597400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>487000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>637000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>677700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>642700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>574300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>787600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>650400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>535400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>365600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>426600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>385000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>471000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>334100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>407200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>364900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>401400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>252500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>294800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>279500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>414200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>363300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>401800</v>
+      </c>
+      <c r="F27" s="3">
         <v>276200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>468800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>514400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>659100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>526200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>678000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>552700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>597400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>487000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>637000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>677700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>642700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>574300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>787600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>650400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>535400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>365600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>426600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>385000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>471000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>334100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>407200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>364900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>401400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>252500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>294800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>279500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>414200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2522,8 +2636,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2563,47 +2683,47 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>12200</v>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>12200</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>310800</v>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>310800</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2614,8 +2734,14 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2706,8 +2832,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2798,8 +2930,14 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2816,14 +2954,14 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>400</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
@@ -2867,14 +3005,14 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>1000</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
@@ -2882,108 +3020,120 @@
         <v>0</v>
       </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>3500</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>363300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>401800</v>
+      </c>
+      <c r="F33" s="3">
         <v>276200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>468800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>514400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>659100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>526200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>678000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>552700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>597400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>487000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>637000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>677700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>642700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>574300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>787600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>650400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>535400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>365600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>426600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>385000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>483200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>334100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>407200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>364900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>712200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>252500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>294800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>279500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>414200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3074,197 +3224,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>363300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>401800</v>
+      </c>
+      <c r="F35" s="3">
         <v>276200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>468800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>514400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>659100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>526200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>678000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>552700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>597400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>487000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>637000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>677700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>642700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>574300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>787600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>650400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>535400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>365600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>426600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>385000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>483200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>334100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>407200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>364900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>712200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>252500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>294800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>279500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>414200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45415</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45324</v>
+      </c>
+      <c r="F38" s="2">
         <v>45233</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45142</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45051</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44960</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44862</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44771</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44680</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44589</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44498</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44407</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44316</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44225</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44134</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44043</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43952</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43861</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43770</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43679</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43588</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43497</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43406</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43315</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43224</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43133</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43042</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42951</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42860</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42769</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3297,8 +3465,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3331,100 +3501,108 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>720700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>537300</v>
+      </c>
+      <c r="F41" s="3">
         <v>365400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>353000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>313100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>381600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>362700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>326300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>335600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>344800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>488700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>313700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>688100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1376600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2199400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2959600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>2673900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>240300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>276100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>259600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>271100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>235500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>260700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>265300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>284000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>267400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>226200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>214200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>206000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>187900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>200200</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3515,376 +3693,406 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>112300</v>
+      </c>
+      <c r="F43" s="3">
         <v>197600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>151700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>50900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>135800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>188100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>93300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>33600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>97400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>120400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>127000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>16600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>90800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>111100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>36200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>17200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>76500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>103200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>61700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>25200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>57800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>114600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>68400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>28600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>108300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>99700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>44300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>10500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>11100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>54600</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6934400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>6994300</v>
+      </c>
+      <c r="F44" s="3">
         <v>7356100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>7531500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>7335800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>6760700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>7144700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>6935900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>6087400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>5614300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>5298900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>5279300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>5099500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>5247500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>5025800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>4391200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>4107300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>4676800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>4496400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>4419600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>4109800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>4097000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>3979100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>3896400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>3594500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>3609000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>3597200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>3463000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>3300100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>3258800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>3488200</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>406900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>366900</v>
+      </c>
+      <c r="F45" s="3">
         <v>352000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>377800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>355700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>302900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>321500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>327500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>280300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>247300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>273900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>272800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>237600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>199400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>197000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>210500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>194000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>184200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>192900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>178300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>177700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>272700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>275900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>287800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>258900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>263100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>230300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>258600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>232400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>220000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>225400</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8097000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>8010700</v>
+      </c>
+      <c r="F46" s="3">
         <v>8271100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>8414000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>8055500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>7581000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>8017000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>7682900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>6736900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>6303800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>6181800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>5992700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>6041700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>6914200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>7533400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>7597400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>6992500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>5177900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>5068500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>4919100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>4583800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>4663000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>4630300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>4517800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>4166000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>4247900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>4153300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>3980000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>3748900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>3677800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>3968500</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3975,100 +4183,112 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17311200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>17186000</v>
+      </c>
+      <c r="F48" s="3">
         <v>16752700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>16379300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>16146700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>15906300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>15396800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>14967400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>14634200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>14439100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>14160500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>13909300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>13614100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>13373300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>13045200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>12675800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>12280900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>12074500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>11770500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>11425800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>11148800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>2970800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>2921900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>2857300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>2758400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>2701300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>2654900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>2574800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>2487300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>2434500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>2388500</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4097,70 +4317,76 @@
         <v>5538300</v>
       </c>
       <c r="L49" s="3">
-        <v>5538400</v>
+        <v>5538300</v>
       </c>
       <c r="M49" s="3">
-        <v>5538400</v>
+        <v>5538300</v>
       </c>
       <c r="N49" s="3">
         <v>5538400</v>
       </c>
       <c r="O49" s="3">
-        <v>5538500</v>
+        <v>5538400</v>
       </c>
       <c r="P49" s="3">
-        <v>5538500</v>
+        <v>5538400</v>
       </c>
       <c r="Q49" s="3">
         <v>5538500</v>
       </c>
       <c r="R49" s="3">
-        <v>5538600</v>
+        <v>5538500</v>
       </c>
       <c r="S49" s="3">
-        <v>5538600</v>
+        <v>5538500</v>
       </c>
       <c r="T49" s="3">
         <v>5538600</v>
       </c>
       <c r="U49" s="3">
+        <v>5538600</v>
+      </c>
+      <c r="V49" s="3">
+        <v>5538600</v>
+      </c>
+      <c r="W49" s="3">
         <v>5538700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>5538800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>5538800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>5538900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>5538900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>5539000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>5539000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>5539100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>5539100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>5539200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>5539200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>5539300</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4251,8 +4477,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4343,100 +4575,112 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>60600</v>
+      </c>
+      <c r="F52" s="3">
         <v>62600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>64000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>63500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>57700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>55000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>50700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>46900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>46100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>44600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>47400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>42400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>36600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>36400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>35700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>36300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>34100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>35100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>33900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>33000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>31400</v>
-      </c>
-      <c r="X52" s="3">
-        <v>29900</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>29900</v>
       </c>
       <c r="Z52" s="3">
         <v>29900</v>
       </c>
       <c r="AA52" s="3">
+        <v>29900</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>29900</v>
+      </c>
+      <c r="AC52" s="3">
         <v>28800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>27400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>26900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>20900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>20800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>20800</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4527,100 +4771,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>31009500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>30795600</v>
+      </c>
+      <c r="F54" s="3">
         <v>30624600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>30395600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>29803900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>29083400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>29007200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>28239300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>26956300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>26327400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>25925300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>25487800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>25236700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>25862600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>26153400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>25847400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>24848300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>22825100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>22412800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>21917500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>21304300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>13204000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>13121000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>12943900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>12493200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>12516900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>12374800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>12120800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>11796400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>11672300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>11917100</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4653,8 +4909,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4687,129 +4945,137 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3472500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3587400</v>
+      </c>
+      <c r="F57" s="3">
         <v>3651800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3681600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3679200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3553000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>4127100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>4358400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>3906900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3738600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3532600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>3370000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>3294400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>3614100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>3770500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>3400600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>2954400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>2860700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>2844200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2727100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>2452900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>2385500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>2336800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>2295000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>2018300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>2009800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>1978000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>1880700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>1622800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>1557600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>1948100</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>769100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>768600</v>
+      </c>
+      <c r="F58" s="3">
         <v>750000</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" s="3">
-        <v>250000</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H58" s="3" t="s">
+      <c r="H58" s="3">
+        <v>250000</v>
+      </c>
+      <c r="I58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K58" s="3">
         <v>900600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>900600</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
@@ -4826,11 +5092,11 @@
       <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R58" s="3">
-        <v>600</v>
-      </c>
-      <c r="S58" s="3">
-        <v>600</v>
+      <c r="R58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T58" s="3">
         <v>600</v>
@@ -4842,405 +5108,435 @@
         <v>600</v>
       </c>
       <c r="W58" s="3">
+        <v>600</v>
+      </c>
+      <c r="X58" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y58" s="3">
         <v>2000</v>
-      </c>
-      <c r="X58" s="3">
-        <v>1900</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>1900</v>
       </c>
       <c r="Z58" s="3">
         <v>1900</v>
       </c>
       <c r="AA58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AB58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AC58" s="3">
         <v>401300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>401500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>401400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>401200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>501000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>501500</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2400200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2369700</v>
+      </c>
+      <c r="F59" s="3">
         <v>2385300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2352300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2171500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2334800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2375600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2307800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2144400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2240800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2207900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>2109100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2021000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2096700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2115700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>2010500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1888300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1682300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1661300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1584600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1503300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>628400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>643500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>618600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>505100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>553800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>558200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>524700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>668100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>564300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>510100</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6641900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6725700</v>
+      </c>
+      <c r="F60" s="3">
         <v>6787100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6033900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>6100700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>5887800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>6502600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>7566800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>6951800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>5979400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>5740500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>5479100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>5315400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>5710800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>5886200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>5411200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>4843200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>4543000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>4506000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>4312300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>3956700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>3015900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>2982200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>2915500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>2525300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>2964900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>2937800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>2806800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>2692000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>2622800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>2959700</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6222400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6231500</v>
+      </c>
+      <c r="F61" s="3">
         <v>6440800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>7295200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>7028800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>7009400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>5985700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>4290700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>3947500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>4172100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>4127400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>4156800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>4130700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>4131000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>4131600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>4089000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>3967200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>2912000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>2762500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>2573500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>2732100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>2862700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>2902400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>2776800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>2862500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>2604600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>2719600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>2683100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>2632100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>2710600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>2673200</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11145100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>11089200</v>
+      </c>
+      <c r="F62" s="3">
         <v>10944800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>10768700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>10739200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>10644400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>10425000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>10193300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>10095400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>9914000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>9867600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>9714800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>9540700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>9359600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>9150100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>8991200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>8828400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>8667600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>8496000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>8282600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>8042800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>908000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>880500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>872700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>869100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>821600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>973200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>943900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>943300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>932600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>922300</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5331,8 +5627,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5423,8 +5725,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5515,100 +5823,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24009300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>24046500</v>
+      </c>
+      <c r="F66" s="3">
         <v>24172700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>24097900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>23868700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>23541600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>22913400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>22050800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>20994700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>20065400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>19735500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>19350700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>18986800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>19201400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>19167900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>18491400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>17638900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>16122600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>15764500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>15168400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>14731600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>6786600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>6765100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>6565000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>6256900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>6391100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>6630600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>6433700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>6267500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>6266000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>6555200</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5641,8 +5961,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5733,8 +6055,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5825,8 +6153,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5917,8 +6251,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6009,100 +6349,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3033000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2799400</v>
+      </c>
+      <c r="F72" s="3">
         <v>2527200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>2380500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>2041100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1656100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>2222800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>2364100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>2157600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>2474000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>2461200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>2429800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>2588000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>3006100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>3346800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>3759000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>3659800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>3162700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>3120700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>3234900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>3074600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>2941100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>2890100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>2928100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>2795600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>2698400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>2334500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>2286100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>2136400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>2015900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>1978000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6193,8 +6545,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6285,8 +6643,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6377,100 +6741,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7000200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>6749100</v>
+      </c>
+      <c r="F76" s="3">
         <v>6451900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>6297700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5935300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5541800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>6093800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>6188500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5961600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>6262000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>6189800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>6137100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>6249900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>6661200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>6985500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>7356100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>7209500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>6702500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>6648300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>6749200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>6572700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>6417400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>6355900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>6378900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>6236300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>6125800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>5744200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>5687100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>5528900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>5406300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>5361900</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6561,197 +6937,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45415</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45324</v>
+      </c>
+      <c r="F80" s="2">
         <v>45233</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45142</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45051</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44960</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44862</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44771</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44680</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44589</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44498</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44407</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44316</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44225</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44134</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44043</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43952</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43861</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43770</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43679</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43588</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43497</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43406</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43315</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43224</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43133</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43042</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42951</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42860</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42769</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>363300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>401800</v>
+      </c>
+      <c r="F81" s="3">
         <v>276200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>468800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>514400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>659100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>526200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>678000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>552700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>597400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>487000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>637000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>677700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>642700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>574300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>787600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>650400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>535400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>365600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>426600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>385000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>483200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>334100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>407200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>364900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>712200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>252500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>294800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>279500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>414200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6784,100 +7178,108 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>232300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>223000</v>
+      </c>
+      <c r="F83" s="3">
         <v>215500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>208400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>201900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>192400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>182800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>177200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>172600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>166400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>162300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>158500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>154100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>149800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>145800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>141000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>137700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>132400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>126500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>123400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>122500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>117800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>114900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>112200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>109300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>105700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>101000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>99000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>98600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>97500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>95400</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6968,8 +7370,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7060,8 +7468,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7152,8 +7566,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7244,8 +7664,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7336,100 +7762,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>663800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>949800</v>
+      </c>
+      <c r="F89" s="3">
         <v>715300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>535600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>191100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>736400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>300200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>498500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>449500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>639100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>909200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>614600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>703000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>492600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>476200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1171000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1736300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>576900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>530600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>556300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>574200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>629400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>416800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>548600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>548600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>659200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>356700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>275800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>510500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>480600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>331100</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7462,100 +7900,108 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-342000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-459700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-472600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-404800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-363100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-482400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-419400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-377200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-281600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-291100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-260900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-240700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-277700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-330400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-273400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-228700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-195400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-266800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-225000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-148300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-144800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-183500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-179900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-206300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-164600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-157800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-174600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-170500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-143500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-154400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-138100</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7646,8 +8092,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7738,100 +8190,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-341200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-458500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-470800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-403100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-361600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-479500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-419200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-375800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-280800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-290100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-258800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-239700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-276900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-328900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-272900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-228100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-195000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-266300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-224500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-147300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-144300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-182500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-179500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-205600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-164000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-157400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-173900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-170300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-143400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-149400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-136200</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7864,100 +8328,108 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-129700</v>
+      </c>
+      <c r="E96" s="3">
+        <v>-129600</v>
+      </c>
+      <c r="F96" s="3">
         <v>-129500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>-129500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>-129400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>-121300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>-123000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>-124200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-125300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-96800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-97300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-98300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-99800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-87300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-88400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-89700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-90600</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-80800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-81600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-82400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-82800</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-75300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>118300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-271900</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-77700</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-70000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-70600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-71000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-71300</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-68900</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-70100</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8048,8 +8520,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8140,8 +8618,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8232,100 +8716,112 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-139200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-319500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-232000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-92600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>102000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-238000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>155500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-132100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-177900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-492800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-475400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-749200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1114600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-986600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-963500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-657200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>892200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-346300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-289500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-420600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-394300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-472100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-242000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-361700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-368100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-460600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-170700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-97300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-349000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-343600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-179700</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8416,96 +8912,108 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>183400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>171800</v>
+      </c>
+      <c r="F102" s="3">
         <v>12400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>40000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-68500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>18800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>36500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-9400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-9200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-143800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>175000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-374400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-688500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-822900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-760200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>285700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>2433600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-35800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>16500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-11500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>35600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-25200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-18700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>16500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>41200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>12000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>8200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>18100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-12300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>15200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
   <si>
     <t>DG</t>
   </si>
@@ -656,419 +656,431 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45506</v>
+      </c>
+      <c r="E7" s="2">
         <v>45415</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45324</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45233</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45142</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45051</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44960</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44862</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44771</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44680</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44589</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44498</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44407</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44316</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44225</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44134</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44043</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43952</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43861</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43770</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43679</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43588</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43497</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43406</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43315</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43224</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43133</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43042</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42951</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42860</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42769</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10210400</v>
+      </c>
+      <c r="E8" s="3">
         <v>9914000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9858500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9694100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9796200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9342800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10202900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9464900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9425700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8751400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8651400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8517800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8650200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8401000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8414500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8199600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8684200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8448400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7157600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6991400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6981800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6623200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6649800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6417500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6443300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6114500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6129400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5903600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5828300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5609600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6009200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5320000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7150900</v>
+      </c>
+      <c r="E9" s="3">
         <v>6921900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6952200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6881600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6751500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6387400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7054600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6579700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6377500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6013000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5951200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5898400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5912500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5645300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5677800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5631400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5866000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5852800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4884900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4926300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4832800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4620900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4578100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4522400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4468400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4252200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4164000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4137200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4037800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3910600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4108500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3732500</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3059500</v>
+      </c>
+      <c r="E10" s="3">
         <v>2992100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2906300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2812500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3044700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2955400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3148300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2885200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3048200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2738400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2700200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2619400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2737700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2755700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2736700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2568200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2818200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2595600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2272700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2065100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2149000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2002300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2071700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1895100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1974900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1862300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1965400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1766500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1790500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1699000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1900700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1587500</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1103,8 +1115,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1201,8 +1214,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1299,8 +1315,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1343,8 +1362,8 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
@@ -1355,17 +1374,17 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>31000</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
@@ -1379,8 +1398,8 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1388,8 +1407,8 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>8</v>
+      <c r="AF14" s="3">
+        <v>0</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
@@ -1397,8 +1416,11 @@
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1495,8 +1517,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1528,204 +1553,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9660400</v>
+      </c>
+      <c r="E17" s="3">
         <v>9367900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9278900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9260600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9103900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8602000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9269700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8729300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8512300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8005200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7854800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7852300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7800600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7492100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7542300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7426500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7641600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7581700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6436800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6500000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6404000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6110900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6011300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5975300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5897800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5624300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5506000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5486200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5335200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5135800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5328600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4927000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>550000</v>
+      </c>
+      <c r="E18" s="3">
         <v>546100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>579600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>433500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>692300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>740800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>933200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>735600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>913400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>746200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>796600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>665500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>849600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>908900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>872200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>773100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1042600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>866700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>720800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>491400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>577800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>512300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>638500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>442200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>545500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>490200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>623400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>417400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>493100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>473800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>680600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>393000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1760,8 +1792,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1784,11 +1817,11 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1835,11 +1868,11 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
@@ -1850,408 +1883,423 @@
         <v>0</v>
       </c>
       <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>788800</v>
+      </c>
+      <c r="E21" s="3">
         <v>778400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>802600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>649000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>900700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>942800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1125500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>917900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1090600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>918700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>963000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>827900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1008100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1063000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1022000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>919000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1183600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1004400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>853300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>617900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>701200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>634700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>756300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>557000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>656600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>599500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>729100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>518400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>592200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>568900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>778200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>488400</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>68100</v>
+      </c>
+      <c r="E22" s="3">
         <v>72400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>77100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>82300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>84300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>83000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>74800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>53700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>43100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>39700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>38500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>39200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>39400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>40400</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>40300</v>
       </c>
       <c r="R22" s="3">
         <v>40300</v>
       </c>
       <c r="S22" s="3">
+        <v>40300</v>
+      </c>
+      <c r="T22" s="3">
         <v>39300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>30500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>25600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>24300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>24800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>25900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>25100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>24600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>25500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>24800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>24300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>24000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>23700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>25000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>25500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>481800</v>
+      </c>
+      <c r="E23" s="3">
         <v>473700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>502500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>351200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>608000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>657800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>858400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>681400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>870300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>706500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>758200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>626400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>810100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>868500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>832000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>732800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1003300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>836300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>695300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>467200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>553000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>486300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>613400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>417600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>519000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>465400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>599200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>393400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>469400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>445300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>655100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>369100</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>107600</v>
+      </c>
+      <c r="E24" s="3">
         <v>110400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>74900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>139100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>143400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>199200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>155300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>192300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>153800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>160700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>139400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>173100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>190700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>189200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>158600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>215700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>185800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>159900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>101600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>126400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>101300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>142400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>83400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>111800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>100600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>197800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>140900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>174600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>165800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>240900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2348,204 +2396,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>374200</v>
+      </c>
+      <c r="E26" s="3">
         <v>363300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>401800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>276200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>468800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>514400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>659100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>526200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>678000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>552700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>597400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>487000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>637000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>677700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>642700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>574300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>787600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>650400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>535400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>365600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>426600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>385000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>471000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>334100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>407200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>364900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>401400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>252500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>294800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>279500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>414200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>374200</v>
+      </c>
+      <c r="E27" s="3">
         <v>363300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>401800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>276200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>468800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>514400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>659100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>526200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>678000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>552700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>597400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>487000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>637000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>677700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>642700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>574300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>787600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>650400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>535400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>365600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>426600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>385000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>471000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>334100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>407200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>364900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>401400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>252500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>294800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>279500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>414200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2642,8 +2699,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2689,8 +2749,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2698,11 +2758,11 @@
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3" t="s">
+      <c r="U29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2710,11 +2770,11 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>12200</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2722,11 +2782,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>310800</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2740,8 +2800,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2838,8 +2901,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2936,8 +3002,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2960,11 +3029,11 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -3011,11 +3080,11 @@
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>1000</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
@@ -3026,114 +3095,120 @@
         <v>0</v>
       </c>
       <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>3500</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>374200</v>
+      </c>
+      <c r="E33" s="3">
         <v>363300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>401800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>276200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>468800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>514400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>659100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>526200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>678000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>552700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>597400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>487000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>637000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>677700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>642700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>574300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>787600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>650400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>535400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>365600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>426600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>385000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>483200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>334100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>407200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>364900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>712200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>252500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>294800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>279500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>414200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3230,209 +3305,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>374200</v>
+      </c>
+      <c r="E35" s="3">
         <v>363300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>401800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>276200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>468800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>514400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>659100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>526200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>678000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>552700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>597400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>487000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>637000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>677700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>642700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>574300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>787600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>650400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>535400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>365600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>426600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>385000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>483200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>334100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>407200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>364900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>712200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>252500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>294800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>279500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>414200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45506</v>
+      </c>
+      <c r="E38" s="2">
         <v>45415</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45324</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45233</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45142</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45051</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44960</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44862</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44771</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44680</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44589</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44498</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44407</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44316</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44225</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44134</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44043</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43952</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43861</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43770</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43679</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43588</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43497</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43406</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43315</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43224</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43133</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43042</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42951</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42860</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42769</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3467,8 +3551,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3503,106 +3588,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1222700</v>
+      </c>
+      <c r="E41" s="3">
         <v>720700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>537300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>365400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>353000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>313100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>381600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>362700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>326300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>335600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>344800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>488700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>313700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>688100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1376600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2199400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2959600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2673900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>240300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>276100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>259600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>271100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>235500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>260700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>265300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>284000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>267400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>226200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>214200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>206000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>187900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>200200</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3699,400 +3788,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>61500</v>
+      </c>
+      <c r="E43" s="3">
         <v>34900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>112300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>197600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>151700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>50900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>135800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>188100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>93300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>33600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>97400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>120400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>127000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>16600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>90800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>111100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>36200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>17200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>76500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>103200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>61700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>25200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>57800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>114600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>68400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>28600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>108300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>99700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>44300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>10500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>11100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>54600</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7000600</v>
+      </c>
+      <c r="E44" s="3">
         <v>6934400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6994300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7356100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7531500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7335800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6760700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7144700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6935900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6087400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5614300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5298900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5279300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5099500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5247500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5025800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4391200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4107300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4676800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4496400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4419600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4109800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4097000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3979100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3896400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3594500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3609000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3597200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3463000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3300100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3258800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3488200</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>439500</v>
+      </c>
+      <c r="E45" s="3">
         <v>406900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>366900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>352000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>377800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>355700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>302900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>321500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>327500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>280300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>247300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>273900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>272800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>237600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>199400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>197000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>210500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>194000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>184200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>192900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>178300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>177700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>272700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>275900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>287800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>258900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>263100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>230300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>258600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>232400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>220000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>225400</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8724200</v>
+      </c>
+      <c r="E46" s="3">
         <v>8097000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8010700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8271100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8414000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8055500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7581000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8017000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7682900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6736900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6303800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6181800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5992700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6041700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6914200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7533400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7597400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6992500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5177900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5068500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4919100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4583800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4663000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4630300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4517800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4166000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4247900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4153300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3980000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3748900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3677800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3968500</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4189,106 +4293,112 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17489800</v>
+      </c>
+      <c r="E48" s="3">
         <v>17311200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>17186000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>16752700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>16379300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>16146700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15906300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15396800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14967400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14634200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14439100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14160500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13909300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13614100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13373300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>13045200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12675800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12280900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12074500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11770500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11425800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>11148800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2970800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2921900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2857300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2758400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2701300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2654900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2574800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2487300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2434500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2388500</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4323,7 +4433,7 @@
         <v>5538300</v>
       </c>
       <c r="N49" s="3">
-        <v>5538400</v>
+        <v>5538300</v>
       </c>
       <c r="O49" s="3">
         <v>5538400</v>
@@ -4332,7 +4442,7 @@
         <v>5538400</v>
       </c>
       <c r="Q49" s="3">
-        <v>5538500</v>
+        <v>5538400</v>
       </c>
       <c r="R49" s="3">
         <v>5538500</v>
@@ -4341,7 +4451,7 @@
         <v>5538500</v>
       </c>
       <c r="T49" s="3">
-        <v>5538600</v>
+        <v>5538500</v>
       </c>
       <c r="U49" s="3">
         <v>5538600</v>
@@ -4350,43 +4460,46 @@
         <v>5538600</v>
       </c>
       <c r="W49" s="3">
+        <v>5538600</v>
+      </c>
+      <c r="X49" s="3">
         <v>5538700</v>
-      </c>
-      <c r="X49" s="3">
-        <v>5538800</v>
       </c>
       <c r="Y49" s="3">
         <v>5538800</v>
       </c>
       <c r="Z49" s="3">
-        <v>5538900</v>
+        <v>5538800</v>
       </c>
       <c r="AA49" s="3">
         <v>5538900</v>
       </c>
       <c r="AB49" s="3">
-        <v>5539000</v>
+        <v>5538900</v>
       </c>
       <c r="AC49" s="3">
         <v>5539000</v>
       </c>
       <c r="AD49" s="3">
-        <v>5539100</v>
+        <v>5539000</v>
       </c>
       <c r="AE49" s="3">
         <v>5539100</v>
       </c>
       <c r="AF49" s="3">
-        <v>5539200</v>
+        <v>5539100</v>
       </c>
       <c r="AG49" s="3">
         <v>5539200</v>
       </c>
       <c r="AH49" s="3">
+        <v>5539200</v>
+      </c>
+      <c r="AI49" s="3">
         <v>5539300</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4483,8 +4596,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4581,79 +4697,82 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>61500</v>
+      </c>
+      <c r="E52" s="3">
         <v>63000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>60600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>62600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>64000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>63500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>57700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>55000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>50700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>46900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>46100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>44600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>47400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>42400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>36600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>36400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>35700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>36300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>34100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>35100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>33900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>33000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>31400</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>29900</v>
       </c>
       <c r="AA52" s="3">
         <v>29900</v>
@@ -4662,25 +4781,28 @@
         <v>29900</v>
       </c>
       <c r="AC52" s="3">
+        <v>29900</v>
+      </c>
+      <c r="AD52" s="3">
         <v>28800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>27400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>26900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>20900</v>
-      </c>
-      <c r="AG52" s="3">
-        <v>20800</v>
       </c>
       <c r="AH52" s="3">
         <v>20800</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>20800</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4777,106 +4899,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>31813800</v>
+      </c>
+      <c r="E54" s="3">
         <v>31009500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>30795600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>30624600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>30395600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>29803900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>29083400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>29007200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>28239300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>26956300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>26327400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>25925300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>25487800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>25236700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>25862600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>26153400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>25847400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>24848300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>22825100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>22412800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>21917500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>21304300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13204000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13121000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12943900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12493200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>12516900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>12374800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>12120800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>11796400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>11672300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>11917100</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4911,8 +5039,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4947,138 +5076,142 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3869300</v>
+      </c>
+      <c r="E57" s="3">
         <v>3472500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3587400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3651800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3681600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3679200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3553000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4127100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4358400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3906900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3738600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3532600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3370000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3294400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3614100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3770500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3400600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2954400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2860700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2844200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2727100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2452900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2385500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2336800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2295000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2018300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2009800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1978000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1880700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1622800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1557600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1948100</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>769200</v>
+      </c>
+      <c r="E58" s="3">
         <v>769100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>768600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>750000</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="H58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>250000</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K58" s="3">
-        <v>900600</v>
+      <c r="K58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L58" s="3">
         <v>900600</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>8</v>
+      <c r="M58" s="3">
+        <v>900600</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>8</v>
@@ -5098,8 +5231,8 @@
       <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T58" s="3">
-        <v>600</v>
+      <c r="T58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U58" s="3">
         <v>600</v>
@@ -5114,10 +5247,10 @@
         <v>600</v>
       </c>
       <c r="Y58" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z58" s="3">
         <v>2000</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>1900</v>
       </c>
       <c r="AA58" s="3">
         <v>1900</v>
@@ -5126,417 +5259,432 @@
         <v>1900</v>
       </c>
       <c r="AC58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AD58" s="3">
         <v>401300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>401500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>401400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>401200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>501000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>501500</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2502700</v>
+      </c>
+      <c r="E59" s="3">
         <v>2400200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2369700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2385300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2352300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2171500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2334800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2375600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2307800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2144400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2240800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2207900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2109100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2021000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2096700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2115700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2010500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1888300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1682300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1661300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1584600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1503300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>628400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>643500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>618600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>505100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>553800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>558200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>524700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>668100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>564300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>510100</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7141200</v>
+      </c>
+      <c r="E60" s="3">
         <v>6641900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6725700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6787100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6033900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6100700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5887800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6502600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7566800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6951800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5979400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5740500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5479100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5315400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5710800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5886200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5411200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4843200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4543000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4506000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4312300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3956700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3015900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2982200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2915500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2525300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2964900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2937800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2806800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2692000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2622800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2959700</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6235200</v>
+      </c>
+      <c r="E61" s="3">
         <v>6222400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6231500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6440800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7295200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7028800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7009400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5985700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4290700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3947500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4172100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4127400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4156800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4130700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4131000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4131600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4089000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3967200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2912000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2762500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2573500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2732100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2862700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2902400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2776800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2862500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2604600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2719600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2683100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2632100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2710600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2673200</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11177200</v>
+      </c>
+      <c r="E62" s="3">
         <v>11145100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>11089200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10944800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10768700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10739200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10644400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10425000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10193300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10095400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9914000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9867600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9714800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9540700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9359600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>9150100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8991200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8828400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8667600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8496000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8282600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8042800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>908000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>880500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>872700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>869100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>821600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>973200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>943900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>943300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>932600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>922300</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5633,8 +5781,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5731,8 +5882,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5829,106 +5983,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24553500</v>
+      </c>
+      <c r="E66" s="3">
         <v>24009300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>24046500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24172700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24097900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>23868700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>23541600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>22913400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>22050800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20994700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20065400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>19735500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19350700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18986800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>19201400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19167900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>18491400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>17638900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>16122600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>15764500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15168400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>14731600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6786600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6765100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6565000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6256900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6391100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6630600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6433700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6267500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6266000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6555200</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5963,8 +6123,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6061,8 +6222,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6159,8 +6323,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6257,8 +6424,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6355,106 +6525,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3277400</v>
+      </c>
+      <c r="E72" s="3">
         <v>3033000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2799400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2527200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2380500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2041100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1656100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2222800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2364100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2157600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2474000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2461200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2429800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2588000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3006100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3346800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3759000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3659800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3162700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3120700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3234900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3074600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2941100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2890100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2928100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2795600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2698400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2334500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2286100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2136400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2015900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1978000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6551,8 +6727,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6649,8 +6828,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6747,106 +6929,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7260200</v>
+      </c>
+      <c r="E76" s="3">
         <v>7000200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6749100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6451900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6297700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5935300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5541800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6093800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6188500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5961600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6262000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6189800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6137100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6249900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6661200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6985500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7356100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7209500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6702500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6648300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6749200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6572700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6417400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6355900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6378900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6236300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6125800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5744200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5687100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5528900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5406300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5361900</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6943,209 +7131,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45506</v>
+      </c>
+      <c r="E80" s="2">
         <v>45415</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45324</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45233</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45142</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45051</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44960</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44862</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44771</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44680</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44589</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44498</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44407</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44316</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44225</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44134</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44043</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43952</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43861</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43770</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43679</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43588</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43497</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43406</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43315</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43224</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43133</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43042</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42951</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42860</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42769</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>374200</v>
+      </c>
+      <c r="E81" s="3">
         <v>363300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>401800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>276200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>468800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>514400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>659100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>526200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>678000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>552700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>597400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>487000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>637000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>677700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>642700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>574300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>787600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>650400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>535400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>365600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>426600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>385000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>483200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>334100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>407200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>364900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>712200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>252500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>294800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>279500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>414200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7180,106 +7377,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>238800</v>
+      </c>
+      <c r="E83" s="3">
         <v>232300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>223000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>215500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>208400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>201900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>192400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>182800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>177200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>172600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>166400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>162300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>158500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>154100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>149800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>145800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>141000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>137700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>132400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>126500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>123400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>122500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>117800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>114900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>112200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>109300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>105700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>101000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>99000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>98600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>97500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>95400</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7376,8 +7577,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7474,8 +7678,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7572,8 +7779,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7670,8 +7880,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7768,106 +7981,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>988900</v>
+      </c>
+      <c r="E89" s="3">
         <v>663800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>949800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>715300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>535600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>191100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>736400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>300200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>498500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>449500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>639100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>909200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>614600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>703000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>492600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>476200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1171000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1736300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>576900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>530600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>556300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>574200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>629400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>416800</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>548600</v>
       </c>
       <c r="AB89" s="3">
         <v>548600</v>
       </c>
       <c r="AC89" s="3">
+        <v>548600</v>
+      </c>
+      <c r="AD89" s="3">
         <v>659200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>356700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>275800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>510500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>480600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>331100</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7902,106 +8121,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-353700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-342000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-459700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-472600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-404800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-363100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-482400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-419400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-377200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-281600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-291100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-260900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-240700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-277700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-330400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-273400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-228700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-195400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-266800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-225000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-148300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-144800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-183500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-179900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-206300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-164600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-157800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-174600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-170500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-143500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-154400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-138100</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8098,8 +8321,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8196,106 +8422,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-353000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-341200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-458500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-470800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-403100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-361600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-479500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-419200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-375800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-280800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-290100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-258800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-239700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-276900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-328900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-272900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-228100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-195000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-266300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-224500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-147300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-144300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-182500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-179500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-205600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-164000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-157400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-173900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-170300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-143400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-149400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-136200</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8330,8 +8562,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8339,97 +8572,100 @@
         <v>-129700</v>
       </c>
       <c r="E96" s="3">
+        <v>-129700</v>
+      </c>
+      <c r="F96" s="3">
         <v>-129600</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-129500</v>
       </c>
       <c r="G96" s="3">
         <v>-129500</v>
       </c>
       <c r="H96" s="3">
+        <v>-129500</v>
+      </c>
+      <c r="I96" s="3">
         <v>-129400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-121300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-123000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-124200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-125300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-96800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-97300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-98300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-99800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-87300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-88400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-89700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-90600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-80800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-81600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-82400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-82800</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-75300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>118300</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-271900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-77700</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-70000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-70600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-71000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-71300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-68900</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-70100</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8526,8 +8762,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8624,8 +8863,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8722,106 +8964,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-133900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-139200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-319500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-232000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-92600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>102000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-238000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>155500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-132100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-177900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-492800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-475400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-749200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1114600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-986600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-963500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-657200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>892200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-346300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-289500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-420600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-394300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-472100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-242000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-361700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-368100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-460600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-170700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-97300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-349000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-343600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-179700</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8918,102 +9166,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>502000</v>
+      </c>
+      <c r="E102" s="3">
         <v>183400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>171800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>40000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-68500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>18800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>36500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-143800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>175000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-374400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-688500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-822900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-760200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>285700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2433600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-35800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>16500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-11500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>35600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-25200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-18700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>16500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>41200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>12000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>8200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>18100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-12300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>15200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
   <si>
     <t>DG</t>
   </si>
@@ -656,431 +656,443 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45597</v>
+      </c>
+      <c r="E7" s="2">
         <v>45506</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45415</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45324</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45233</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45142</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45051</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44960</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44862</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44771</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44680</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44589</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44498</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44407</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44316</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44225</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44134</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44043</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43952</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43861</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43770</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43679</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43588</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43497</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43406</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43315</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43224</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43133</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43042</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42951</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42860</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42769</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10183400</v>
+      </c>
+      <c r="E8" s="3">
         <v>10210400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9914000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9858500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9694100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9796200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9342800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10202900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9464900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9425700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8751400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8651400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8517800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8650200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8401000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8414500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8199600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8684200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8448400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7157600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6991400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6981800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6623200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6649800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6417500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6443300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6114500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6129400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5903600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5828300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5609600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6009200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5320000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7247100</v>
+      </c>
+      <c r="E9" s="3">
         <v>7150900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6921900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6952200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6881600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6751500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6387400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7054600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6579700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6377500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6013000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5951200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5898400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5912500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5645300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5677800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5631400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5866000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5852800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4884900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4926300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4832800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4620900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4578100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4522400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4468400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4252200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4164000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4137200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4037800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3910600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4108500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3732500</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2936300</v>
+      </c>
+      <c r="E10" s="3">
         <v>3059500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2992100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2906300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2812500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3044700</v>
       </c>
-      <c r="I10" s="3">
-        <v>2955400</v>
-      </c>
       <c r="J10" s="3">
+        <v>2955500</v>
+      </c>
+      <c r="K10" s="3">
         <v>3148300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2885200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3048200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2738400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2700200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2619400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2737700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2755700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2736700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2568200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2818200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2595600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2272700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2065100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2149000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2002300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2071700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1895100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1974900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1862300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1965400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1766500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1790500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1699000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1900700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1587500</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1116,8 +1128,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1217,8 +1230,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1318,31 +1334,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>6700</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1365,8 +1384,8 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1377,18 +1396,18 @@
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>31000</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1401,8 +1420,8 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
@@ -1410,8 +1429,8 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
+      <c r="AG14" s="3">
+        <v>0</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
@@ -1419,31 +1438,34 @@
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>247000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>238800</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>232300</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>223000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>215500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>208400</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>201900</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1520,8 +1542,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1554,210 +1579,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9859600</v>
+      </c>
+      <c r="E17" s="3">
         <v>9660400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9367900</v>
       </c>
-      <c r="F17" s="3">
-        <v>9278900</v>
-      </c>
       <c r="G17" s="3">
+        <v>9272200</v>
+      </c>
+      <c r="H17" s="3">
         <v>9260600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9103900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8602000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9269700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8729300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8512300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8005200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7854800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7852300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7800600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7492100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7542300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7426500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7641600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7581700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6436800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6500000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6404000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6110900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6011300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5975300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5897800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5624300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5506000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5486200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5335200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5135800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5328600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4927000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>323800</v>
+      </c>
+      <c r="E18" s="3">
         <v>550000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>546100</v>
       </c>
-      <c r="F18" s="3">
-        <v>579600</v>
-      </c>
       <c r="G18" s="3">
+        <v>586400</v>
+      </c>
+      <c r="H18" s="3">
         <v>433500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>692300</v>
       </c>
-      <c r="I18" s="3">
-        <v>740800</v>
-      </c>
       <c r="J18" s="3">
+        <v>740900</v>
+      </c>
+      <c r="K18" s="3">
         <v>933200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>735600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>913400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>746200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>796600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>665500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>849600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>908900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>872200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>773100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1042600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>866700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>720800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>491400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>577800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>512300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>638500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>442200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>545500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>490200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>623400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>417400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>493100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>473800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>680600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>393000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1793,38 +1825,39 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1871,11 +1904,11 @@
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
@@ -1886,420 +1919,435 @@
         <v>0</v>
       </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>570800</v>
+      </c>
+      <c r="E21" s="3">
         <v>788800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>778400</v>
       </c>
-      <c r="F21" s="3">
-        <v>802600</v>
-      </c>
       <c r="G21" s="3">
+        <v>809300</v>
+      </c>
+      <c r="H21" s="3">
         <v>649000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>900700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>942800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1125500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>917900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1090600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>918700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>963000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>827900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1008100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1063000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1022000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>919000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1183600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1004400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>853300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>617900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>701200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>634700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>756300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>557000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>656600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>599500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>729100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>518400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>592200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>568900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>778200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>488400</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>67800</v>
+      </c>
+      <c r="E22" s="3">
         <v>68100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>72400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>77100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>82300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>84300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>83000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>74800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>53700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>43100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>39700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>38500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>39200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>39400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>40400</v>
-      </c>
-      <c r="R22" s="3">
-        <v>40300</v>
       </c>
       <c r="S22" s="3">
         <v>40300</v>
       </c>
       <c r="T22" s="3">
+        <v>40300</v>
+      </c>
+      <c r="U22" s="3">
         <v>39300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>30500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>25600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>24300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>24800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>25900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>25100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>24600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>25500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>24800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>24300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>24000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>23700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>25000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>25500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>256000</v>
+      </c>
+      <c r="E23" s="3">
         <v>481800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>473700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>502500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>351200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>608000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>657800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>858400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>681400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>870300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>706500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>758200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>626400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>810100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>868500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>832000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>732800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1003300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>836300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>695300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>467200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>553000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>486300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>613400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>417600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>519000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>465400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>599200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>393400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>469400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>445300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>655100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>369100</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>59400</v>
+      </c>
+      <c r="E24" s="3">
         <v>107600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>110400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>74900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>139100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>143400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>199200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>155300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>192300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>153800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>160700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>139400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>173100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>190700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>189200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>158600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>215700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>185800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>159900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>101600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>126400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>101300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>142400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>83400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>111800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>100600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>197800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>140900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>174600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>165800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>240900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,210 +2447,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>196500</v>
+      </c>
+      <c r="E26" s="3">
         <v>374200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>363300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>401800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>276200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>468800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>514400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>659100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>526200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>678000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>552700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>597400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>487000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>637000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>677700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>642700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>574300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>787600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>650400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>535400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>365600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>426600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>385000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>471000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>334100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>407200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>364900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>401400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>252500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>294800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>279500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>414200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>196500</v>
+      </c>
+      <c r="E27" s="3">
         <v>374200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>363300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>401800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>276200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>468800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>514400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>659100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>526200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>678000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>552700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>597400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>487000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>637000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>677700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>642700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>574300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>787600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>650400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>535400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>365600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>426600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>385000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>471000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>334100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>407200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>364900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>401400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>252500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>294800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>279500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>414200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2702,8 +2759,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2752,8 +2812,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2761,11 +2821,11 @@
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2773,24 +2833,24 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>12200</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>310800</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2803,8 +2863,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2904,8 +2967,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3005,38 +3071,41 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -3083,11 +3152,11 @@
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>1000</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
@@ -3098,117 +3167,123 @@
         <v>0</v>
       </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>3500</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>196500</v>
+      </c>
+      <c r="E33" s="3">
         <v>374200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>363300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>401800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>276200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>468800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>514400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>659100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>526200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>678000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>552700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>597400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>487000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>637000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>677700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>642700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>574300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>787600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>650400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>535400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>365600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>426600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>385000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>483200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>334100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>407200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>364900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>712200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>252500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>294800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>279500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>414200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3308,215 +3383,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>196500</v>
+      </c>
+      <c r="E35" s="3">
         <v>374200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>363300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>401800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>276200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>468800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>514400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>659100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>526200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>678000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>552700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>597400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>487000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>637000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>677700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>642700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>574300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>787600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>650400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>535400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>365600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>426600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>385000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>483200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>334100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>407200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>364900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>712200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>252500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>294800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>279500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>414200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45597</v>
+      </c>
+      <c r="E38" s="2">
         <v>45506</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45415</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45324</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45233</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45142</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45051</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44960</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44862</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44771</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44680</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44589</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44498</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44407</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44316</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44225</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44134</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44043</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43952</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43861</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43770</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43679</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43588</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43497</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43406</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43315</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43224</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43133</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43042</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42951</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42860</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42769</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3552,8 +3636,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3589,109 +3674,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>537300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1222700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>720700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>537300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>365400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>353000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>313100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>381600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>362700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>326300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>335600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>344800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>488700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>313700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>688100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1376600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2199400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2959600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2673900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>240300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>276100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>259600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>271100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>235500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>260700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>265300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>284000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>267400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>226200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>214200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>206000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>187900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>200200</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3791,435 +3880,450 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>115700</v>
+      </c>
+      <c r="E43" s="3">
         <v>61500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>34900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>112300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>197600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>151700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>50900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>135800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>188100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>93300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>33600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>97400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>120400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>127000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>16600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>90800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>111100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>36200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>17200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>76500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>103200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>61700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>25200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>57800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>114600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>68400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>28600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>108300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>99700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>44300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>10500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>11100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>54600</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7119000</v>
+      </c>
+      <c r="E44" s="3">
         <v>7000600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6934400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6994300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7356100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7531500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7335800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6760700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7144700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6935900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6087400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5614300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5298900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5279300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5099500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5247500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5025800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4391200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4107300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4676800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4496400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4419600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4109800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4097000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3979100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3896400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3594500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3609000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3597200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3463000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3300100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3258800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3488200</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>439500</v>
-      </c>
-      <c r="E45" s="3">
-        <v>406900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>366900</v>
-      </c>
-      <c r="G45" s="3">
-        <v>352000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>377800</v>
-      </c>
-      <c r="I45" s="3">
-        <v>355700</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>302900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>321500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>327500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>280300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>247300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>273900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>272800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>237600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>199400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>197000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>210500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>194000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>184200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>192900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>178300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>177700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>272700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>275900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>287800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>258900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>263100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>230300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>258600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>232400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>220000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>225400</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8176500</v>
+      </c>
+      <c r="E46" s="3">
         <v>8724200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8097000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8010700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8271100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8414000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8055500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7581000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8017000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7682900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6736900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6303800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6181800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5992700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6041700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6914200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7533400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7597400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6992500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5177900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5068500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4919100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4583800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4663000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4630300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4517800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4166000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4247900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4153300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3980000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3748900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3677800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3968500</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4296,109 +4400,115 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17686600</v>
+      </c>
+      <c r="E48" s="3">
         <v>17489800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>17311200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>17186000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>16752700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>16379300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>16146700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15906300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15396800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14967400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14634200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14439100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>14160500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13909300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13614100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>13373300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13045200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12675800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12280900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12074500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11770500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>11425800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>11148800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2970800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2921900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2857300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2758400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2701300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2654900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2574800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2487300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2434500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2388500</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4436,7 +4546,7 @@
         <v>5538300</v>
       </c>
       <c r="O49" s="3">
-        <v>5538400</v>
+        <v>5538300</v>
       </c>
       <c r="P49" s="3">
         <v>5538400</v>
@@ -4445,7 +4555,7 @@
         <v>5538400</v>
       </c>
       <c r="R49" s="3">
-        <v>5538500</v>
+        <v>5538400</v>
       </c>
       <c r="S49" s="3">
         <v>5538500</v>
@@ -4454,7 +4564,7 @@
         <v>5538500</v>
       </c>
       <c r="U49" s="3">
-        <v>5538600</v>
+        <v>5538500</v>
       </c>
       <c r="V49" s="3">
         <v>5538600</v>
@@ -4463,43 +4573,46 @@
         <v>5538600</v>
       </c>
       <c r="X49" s="3">
+        <v>5538600</v>
+      </c>
+      <c r="Y49" s="3">
         <v>5538700</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>5538800</v>
       </c>
       <c r="Z49" s="3">
         <v>5538800</v>
       </c>
       <c r="AA49" s="3">
-        <v>5538900</v>
+        <v>5538800</v>
       </c>
       <c r="AB49" s="3">
         <v>5538900</v>
       </c>
       <c r="AC49" s="3">
-        <v>5539000</v>
+        <v>5538900</v>
       </c>
       <c r="AD49" s="3">
         <v>5539000</v>
       </c>
       <c r="AE49" s="3">
-        <v>5539100</v>
+        <v>5539000</v>
       </c>
       <c r="AF49" s="3">
         <v>5539100</v>
       </c>
       <c r="AG49" s="3">
-        <v>5539200</v>
+        <v>5539100</v>
       </c>
       <c r="AH49" s="3">
         <v>5539200</v>
       </c>
       <c r="AI49" s="3">
+        <v>5539200</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>5539300</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4599,8 +4712,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4700,82 +4816,85 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E52" s="3">
         <v>61500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>63000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>60600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>62600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>64000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>63500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>57700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>55000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>50700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>46900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>46100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>44600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>47400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>42400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>36600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>36400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>35700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>36300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>34100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>35100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>33900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>33000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>31400</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>29900</v>
       </c>
       <c r="AB52" s="3">
         <v>29900</v>
@@ -4784,25 +4903,28 @@
         <v>29900</v>
       </c>
       <c r="AD52" s="3">
+        <v>29900</v>
+      </c>
+      <c r="AE52" s="3">
         <v>28800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>27400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>26900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>20900</v>
-      </c>
-      <c r="AH52" s="3">
-        <v>20800</v>
       </c>
       <c r="AI52" s="3">
         <v>20800</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>20800</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4902,109 +5024,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>31460400</v>
+      </c>
+      <c r="E54" s="3">
         <v>31813800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>31009500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>30795600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>30624600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>30395600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>29803900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>29083400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>29007200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>28239300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>26956300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>26327400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>25925300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>25487800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>25236700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>25862600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>26153400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>25847400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>24848300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>22825100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>22412800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>21917500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>21304300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13204000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>13121000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12943900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>12493200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>12516900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>12374800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>12120800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>11796400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>11672300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>11917100</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5040,8 +5168,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5077,144 +5206,148 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4045400</v>
+      </c>
+      <c r="E57" s="3">
         <v>3869300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3472500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3587400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3651800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3681600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3679200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3553000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4127100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4358400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3906900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3738600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3532600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3370000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3294400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3614100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3770500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3400600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2954400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2860700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2844200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2727100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2452900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2385500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2336800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2295000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2018300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2009800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1978000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1880700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1622800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1557600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1948100</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>769200</v>
+        <v>1964400</v>
       </c>
       <c r="E58" s="3">
-        <v>769100</v>
+        <v>2194900</v>
       </c>
       <c r="F58" s="3">
-        <v>768600</v>
+        <v>2176100</v>
       </c>
       <c r="G58" s="3">
-        <v>750000</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>8</v>
+        <v>2155700</v>
+      </c>
+      <c r="H58" s="3">
+        <v>2105300</v>
       </c>
       <c r="I58" s="3">
-        <v>250000</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>8</v>
+        <v>1331400</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1561800</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L58" s="3">
-        <v>900600</v>
+      <c r="L58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M58" s="3">
         <v>900600</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>8</v>
+      <c r="N58" s="3">
+        <v>900600</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>8</v>
@@ -5234,8 +5367,8 @@
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U58" s="3">
-        <v>600</v>
+      <c r="U58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V58" s="3">
         <v>600</v>
@@ -5250,10 +5383,10 @@
         <v>600</v>
       </c>
       <c r="Z58" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA58" s="3">
         <v>2000</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>1900</v>
       </c>
       <c r="AB58" s="3">
         <v>1900</v>
@@ -5262,429 +5395,444 @@
         <v>1900</v>
       </c>
       <c r="AD58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AE58" s="3">
         <v>401300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>401500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>401400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>401200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>501000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>501500</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2502700</v>
+        <v>14500</v>
       </c>
       <c r="E59" s="3">
-        <v>2400200</v>
+        <v>12200</v>
       </c>
       <c r="F59" s="3">
-        <v>2369700</v>
+        <v>17200</v>
       </c>
       <c r="G59" s="3">
-        <v>2385300</v>
+        <v>410000</v>
       </c>
       <c r="H59" s="3">
-        <v>2352300</v>
+        <v>9200</v>
       </c>
       <c r="I59" s="3">
-        <v>2171500</v>
+        <v>16900</v>
       </c>
       <c r="J59" s="3">
+        <v>11000</v>
+      </c>
+      <c r="K59" s="3">
         <v>2334800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2375600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2307800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2144400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2240800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2207900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2109100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2021000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2096700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2115700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2010500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1888300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1682300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1661300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1584600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1503300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>628400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>643500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>618600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>505100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>553800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>558200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>524700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>668100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>564300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>510100</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7110700</v>
+      </c>
+      <c r="E60" s="3">
         <v>7141200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6641900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6725700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6787100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6033900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6100700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5887800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6502600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7566800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6951800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5979400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5740500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5479100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5315400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5710800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5886200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5411200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4843200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4543000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4506000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4312300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3956700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3015900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2982200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2915500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2525300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2964900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2937800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2806800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2692000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2622800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2959700</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>6235200</v>
+        <v>15601800</v>
       </c>
       <c r="E61" s="3">
-        <v>6222400</v>
+        <v>16019100</v>
       </c>
       <c r="F61" s="3">
-        <v>6231500</v>
+        <v>15945700</v>
       </c>
       <c r="G61" s="3">
-        <v>6440800</v>
+        <v>15935000</v>
       </c>
       <c r="H61" s="3">
-        <v>7295200</v>
+        <v>15981400</v>
       </c>
       <c r="I61" s="3">
-        <v>7028800</v>
+        <v>16704400</v>
       </c>
       <c r="J61" s="3">
+        <v>16428600</v>
+      </c>
+      <c r="K61" s="3">
         <v>7009400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5985700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4290700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3947500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4172100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4127400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4156800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4130700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4131000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4131600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4089000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3967200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2912000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2762500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2573500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2732100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2862700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2902400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2776800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2862500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2604600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2719600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2683100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2632100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2710600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2673200</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>11177200</v>
+        <v>267300</v>
       </c>
       <c r="E62" s="3">
-        <v>11145100</v>
+        <v>254400</v>
       </c>
       <c r="F62" s="3">
-        <v>11089200</v>
+        <v>264100</v>
       </c>
       <c r="G62" s="3">
-        <v>10944800</v>
+        <v>251900</v>
       </c>
       <c r="H62" s="3">
-        <v>10768700</v>
+        <v>252100</v>
       </c>
       <c r="I62" s="3">
-        <v>10739200</v>
+        <v>240400</v>
       </c>
       <c r="J62" s="3">
+        <v>228000</v>
+      </c>
+      <c r="K62" s="3">
         <v>10644400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10425000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10193300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10095400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9914000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9867600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9714800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9540700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>9359600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>9150100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8991200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8828400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8667600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8496000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8282600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8042800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>908000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>880500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>872700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>869100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>821600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>973200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>943900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>943300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>932600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>922300</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5784,8 +5932,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5885,8 +6036,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5986,109 +6140,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24117800</v>
+      </c>
+      <c r="E66" s="3">
         <v>24553500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>24009300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24046500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24172700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>24097900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>23868700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>23541600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>22913400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>22050800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20994700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20065400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19735500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19350700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18986800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19201400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19167900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>18491400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>17638900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>16122600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15764500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>15168400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>14731600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6786600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6765100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6565000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6256900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6391100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6630600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6433700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6267500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6266000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6555200</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6124,8 +6284,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6225,8 +6386,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6326,8 +6490,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6427,8 +6594,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6528,109 +6698,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3344200</v>
+      </c>
+      <c r="E72" s="3">
         <v>3277400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3033000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2799400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2527200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2380500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2041100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1656100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2222800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2364100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2157600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2474000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2461200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2429800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2588000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3006100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3346800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3759000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3659800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3162700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3120700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3234900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3074600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2941100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2890100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2928100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2795600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2698400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2334500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2286100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2136400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2015900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1978000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6730,8 +6906,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6831,8 +7010,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6932,109 +7114,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7342600</v>
+      </c>
+      <c r="E76" s="3">
         <v>7260200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7000200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6749100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6451900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6297700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5935300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5541800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6093800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6188500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5961600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6262000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6189800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6137100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6249900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6661200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6985500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7356100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7209500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6702500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6648300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6749200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6572700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6417400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6355900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6378900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6236300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6125800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5744200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5687100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5528900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5406300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5361900</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7134,215 +7322,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45597</v>
+      </c>
+      <c r="E80" s="2">
         <v>45506</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45415</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45324</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45233</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45142</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45051</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44960</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44862</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44771</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44680</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44589</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44498</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44407</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44316</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44225</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44134</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44043</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43952</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43861</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43770</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43679</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43588</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43497</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43406</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43315</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43224</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43133</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43042</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42951</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42860</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42769</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>196500</v>
+      </c>
+      <c r="E81" s="3">
         <v>374200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>363300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>401800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>276200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>468800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>514400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>659100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>526200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>678000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>552700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>597400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>487000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>637000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>677700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>642700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>574300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>787600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>650400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>535400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>365600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>426600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>385000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>483200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>334100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>407200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>364900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>712200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>252500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>294800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>279500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>414200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7378,109 +7575,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>238800</v>
+        <v>215500</v>
       </c>
       <c r="E83" s="3">
-        <v>232300</v>
+        <v>208400</v>
       </c>
       <c r="F83" s="3">
-        <v>223000</v>
+        <v>201900</v>
       </c>
       <c r="G83" s="3">
-        <v>215500</v>
+        <v>192400</v>
       </c>
       <c r="H83" s="3">
-        <v>208400</v>
+        <v>182800</v>
       </c>
       <c r="I83" s="3">
-        <v>201900</v>
+        <v>177200</v>
       </c>
       <c r="J83" s="3">
+        <v>172600</v>
+      </c>
+      <c r="K83" s="3">
         <v>192400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>182800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>177200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>172600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>166400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>162300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>158500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>154100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>149800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>145800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>141000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>137700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>132400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>126500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>123400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>122500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>117800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>114900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>112200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>109300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>105700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>101000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>99000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>98600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>97500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>95400</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7580,8 +7781,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7681,8 +7885,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7782,8 +7989,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7883,8 +8093,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7984,109 +8197,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>542400</v>
+      </c>
+      <c r="E89" s="3">
         <v>988900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>663800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>949800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>715300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>535600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>191100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>736400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>300200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>498500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>449500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>639100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>909200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>614600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>703000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>492600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>476200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1171000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1736300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>576900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>530600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>556300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>574200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>629400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>416800</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>548600</v>
       </c>
       <c r="AC89" s="3">
         <v>548600</v>
       </c>
       <c r="AD89" s="3">
+        <v>548600</v>
+      </c>
+      <c r="AE89" s="3">
         <v>659200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>356700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>275800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>510500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>480600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>331100</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8122,109 +8341,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-341400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-353700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-342000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-459700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-472600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-404800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-363100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-482400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-419400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-377200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-281600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-291100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-260900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-240700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-277700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-330400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-273400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-228700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-195400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-266800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-225000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-148300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-144800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-183500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-179900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-206300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-164600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-157800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-174600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-170500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-143500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-154400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-138100</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8324,8 +8547,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8425,109 +8651,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-340800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-353000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-341200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-458500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-470800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-403100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-361600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-479500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-419200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-375800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-280800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-290100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-258800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-239700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-276900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-328900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-272900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-228100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-195000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-266300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-224500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-147300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-144300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-182500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-179500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-205600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-164000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-157400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-173900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-170300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-143400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-149400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-136200</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8563,109 +8795,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-129700</v>
+        <v>129800</v>
       </c>
       <c r="E96" s="3">
-        <v>-129700</v>
+        <v>129700</v>
       </c>
       <c r="F96" s="3">
-        <v>-129600</v>
+        <v>129700</v>
       </c>
       <c r="G96" s="3">
-        <v>-129500</v>
+        <v>129600</v>
       </c>
       <c r="H96" s="3">
-        <v>-129500</v>
+        <v>129500</v>
       </c>
       <c r="I96" s="3">
-        <v>-129400</v>
+        <v>129500</v>
       </c>
       <c r="J96" s="3">
+        <v>129400</v>
+      </c>
+      <c r="K96" s="3">
         <v>-121300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-123000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-124200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-125300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-96800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-97300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-98300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-99800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-87300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-88400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-89700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-90600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-80800</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-81600</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-82400</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-82800</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-75300</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>118300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-271900</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-77700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-70000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-70600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-71000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-71300</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-68900</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-70100</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8765,8 +9001,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8866,8 +9105,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8967,132 +9209,138 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-887100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-133900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-139200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-319500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-232000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-92600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>102000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-238000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>155500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-132100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-177900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-492800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-475400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-749200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1114600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-986600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-963500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-657200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>892200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-346300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-289500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-420600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-394300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-472100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-242000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-361700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-368100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-460600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-170700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-97300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-349000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-343600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-179700</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9169,105 +9417,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-685400</v>
+      </c>
+      <c r="E102" s="3">
         <v>502000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>183400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>171800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>40000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-68500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>18800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>36500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-9200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-143800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>175000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-374400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-688500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-822900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-760200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>285700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2433600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-35800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>16500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-11500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>35600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-25200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-18700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>16500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>41200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>12000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>8200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>18100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-12300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>15200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="92">
   <si>
     <t>DG</t>
   </si>
@@ -656,443 +656,455 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
         <v>45597</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45506</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45415</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45324</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45233</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45142</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45051</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44960</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44862</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44771</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44680</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44589</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44498</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44407</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44316</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44225</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44134</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44043</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43952</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43861</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43770</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43679</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43588</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43497</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43406</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43315</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43224</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43133</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43042</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42951</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42860</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42769</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10304500</v>
+      </c>
+      <c r="E8" s="3">
         <v>10183400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10210400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9914000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9858500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9694100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9796200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9342800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10202900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9464900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9425700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8751400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8651400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8517800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8650200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8401000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8414500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8199600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8684200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8448400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7157600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6991400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6981800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6623200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6649800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6417500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6443300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6114500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6129400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5903600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5828300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5609600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6009200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5320000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7274900</v>
+      </c>
+      <c r="E9" s="3">
         <v>7247100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7150900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6921900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6952200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6881600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6751500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6387400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7054600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6579700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6377500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6013000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5951200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5898400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5912500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5645300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5677800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5631400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5866000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5852800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4884900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4926300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4832800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4620900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4578100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4522400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4468400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4252200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4164000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4137200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4037800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3910600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4108500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3732500</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3029600</v>
+      </c>
+      <c r="E10" s="3">
         <v>2936300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3059500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2992100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2906300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2812500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3044700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2955500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3148300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2885200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3048200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2738400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2700200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2619400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2737700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2755700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2736700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2568200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2818200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2595600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2272700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2065100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2149000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2002300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2071700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1895100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1974900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1862300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1965400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1766500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1790500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1699000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1900700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1587500</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1129,8 +1141,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1233,8 +1246,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1337,8 +1353,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1351,20 +1370,20 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>6700</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1387,8 +1406,8 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1399,18 +1418,18 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>31000</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1423,8 +1442,8 @@
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
@@ -1432,8 +1451,8 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
+      <c r="AH14" s="3">
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="s">
         <v>8</v>
@@ -1441,35 +1460,38 @@
       <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>253600</v>
+      </c>
+      <c r="E15" s="3">
         <v>247000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>238800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>232300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>223000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>215500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>208400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>201900</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1545,8 +1567,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1580,216 +1605,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10010300</v>
+      </c>
+      <c r="E17" s="3">
         <v>9859600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9660400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9367900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9272200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9260600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9103900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8602000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9269700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8729300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8512300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8005200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7854800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7852300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7800600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7492100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7542300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7426500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7641600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7581700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6436800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6500000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6404000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6110900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6011300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5975300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5897800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5624300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5506000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5486200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5335200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5135800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5328600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4927000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>294200</v>
+      </c>
+      <c r="E18" s="3">
         <v>323800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>550000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>546100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>586400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>433500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>692300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>740900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>933200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>735600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>913400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>746200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>796600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>665500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>849600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>908900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>872200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>773100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1042600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>866700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>720800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>491400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>577800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>512300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>638500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>442200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>545500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>490200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>623400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>417400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>493100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>473800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>680600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>393000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1826,8 +1858,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1852,15 +1885,15 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-400</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1907,11 +1940,11 @@
         <v>0</v>
       </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
@@ -1922,432 +1955,447 @@
         <v>0</v>
       </c>
       <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI20" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>547800</v>
+      </c>
+      <c r="E21" s="3">
         <v>570800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>788800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>778400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>809300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>649000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>900700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>942800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1125500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>917900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1090600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>918700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>963000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>827900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1008100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1063000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1022000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>919000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1183600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1004400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>853300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>617900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>701200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>634700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>756300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>557000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>656600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>599500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>729100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>518400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>592200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>568900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>778200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>488400</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>65900</v>
+      </c>
+      <c r="E22" s="3">
         <v>67800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>68100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>72400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>77100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>82300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>84300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>83000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>74800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>53700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>43100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>39700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>38500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>39200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>39400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>40400</v>
-      </c>
-      <c r="S22" s="3">
-        <v>40300</v>
       </c>
       <c r="T22" s="3">
         <v>40300</v>
       </c>
       <c r="U22" s="3">
+        <v>40300</v>
+      </c>
+      <c r="V22" s="3">
         <v>39300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>30500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>25600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>24300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>24800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>25900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>25100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>24600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>25500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>24800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>24300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>24000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>23700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>25000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>25500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>228300</v>
+      </c>
+      <c r="E23" s="3">
         <v>256000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>481800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>473700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>502500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>351200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>608000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>657800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>858400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>681400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>870300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>706500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>758200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>626400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>810100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>868500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>832000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>732800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1003300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>836300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>695300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>467200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>553000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>486300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>613400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>417600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>519000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>465400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>599200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>393400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>469400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>445300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>655100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>369100</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E24" s="3">
         <v>59400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>107600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>110400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>74900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>139100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>143400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>199200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>155300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>192300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>153800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>160700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>139400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>173100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>190700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>189200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>158600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>215700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>185800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>159900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>101600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>126400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>101300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>142400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>83400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>111800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>100600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>197800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>140900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>174600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>165800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>240900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2450,216 +2498,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>191200</v>
+      </c>
+      <c r="E26" s="3">
         <v>196500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>374200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>363300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>401800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>276200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>468800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>514400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>659100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>526200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>678000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>552700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>597400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>487000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>637000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>677700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>642700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>574300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>787600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>650400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>535400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>365600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>426600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>385000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>471000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>334100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>407200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>364900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>401400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>252500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>294800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>279500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>414200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>191200</v>
+      </c>
+      <c r="E27" s="3">
         <v>196500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>374200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>363300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>401800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>276200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>468800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>514400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>659100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>526200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>678000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>552700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>597400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>487000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>637000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>677700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>642700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>574300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>787600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>650400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>535400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>365600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>426600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>385000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>471000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>334100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>407200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>364900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>401400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>252500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>294800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>279500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>414200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2762,8 +2819,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2815,8 +2875,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2824,11 +2884,11 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2836,24 +2896,24 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>12200</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>310800</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2866,8 +2926,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2970,8 +3033,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3074,8 +3140,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3100,15 +3169,15 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>400</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -3155,11 +3224,11 @@
         <v>0</v>
       </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>1000</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
@@ -3170,120 +3239,126 @@
         <v>0</v>
       </c>
       <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
         <v>3500</v>
       </c>
-      <c r="AI32" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>191200</v>
+      </c>
+      <c r="E33" s="3">
         <v>196500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>374200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>363300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>401800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>276200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>468800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>514400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>659100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>526200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>678000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>552700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>597400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>487000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>637000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>677700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>642700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>574300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>787600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>650400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>535400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>365600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>426600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>385000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>483200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>334100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>407200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>364900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>712200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>252500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>294800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>279500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>414200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3386,221 +3461,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>191200</v>
+      </c>
+      <c r="E35" s="3">
         <v>196500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>374200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>363300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>401800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>276200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>468800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>514400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>659100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>526200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>678000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>552700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>597400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>487000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>637000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>677700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>642700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>574300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>787600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>650400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>535400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>365600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>426600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>385000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>483200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>334100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>407200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>364900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>712200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>252500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>294800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>279500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>414200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
         <v>45597</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45506</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45415</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45324</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45233</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45142</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45051</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44960</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44862</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44771</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44680</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44589</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44498</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44407</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44316</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44225</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44134</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44043</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43952</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43861</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43770</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43679</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43588</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43497</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43406</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43315</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43224</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43133</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43042</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42951</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42860</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42769</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3637,8 +3721,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3675,112 +3760,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>932600</v>
+      </c>
+      <c r="E41" s="3">
         <v>537300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1222700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>720700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>537300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>365400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>353000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>313100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>381600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>362700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>326300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>335600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>344800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>488700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>313700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>688100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1376600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2199400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2959600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2673900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>240300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>276100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>259600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>271100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>235500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>260700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>265300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>284000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>267400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>226200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>214200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>206000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>187900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>200200</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3883,216 +3972,225 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>127100</v>
+      </c>
+      <c r="E43" s="3">
         <v>115700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>61500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>34900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>112300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>197600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>151700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>50900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>135800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>188100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>93300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>33600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>97400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>120400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>127000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>16600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>90800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>111100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>36200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>17200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>76500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>103200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>61700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>25200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>57800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>114600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>68400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>28600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>108300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>99700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>44300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>10500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>11100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>54600</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6711200</v>
+      </c>
+      <c r="E44" s="3">
         <v>7119000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7000600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6934400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6994300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7356100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7531500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7335800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6760700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7144700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6935900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6087400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5614300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5298900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5279300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5099500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5247500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5025800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4391200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4107300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4676800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4496400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4419600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4109800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4097000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3979100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3896400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3594500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3609000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3597200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3463000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3300100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3258800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>3488200</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4117,190 +4215,196 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>302900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>321500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>327500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>280300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>247300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>273900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>272800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>237600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>199400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>197000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>210500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>194000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>184200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>192900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>178300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>177700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>272700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>275900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>287800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>258900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>263100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>230300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>258600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>232400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>220000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>225400</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8163900</v>
+      </c>
+      <c r="E46" s="3">
         <v>8176500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8724200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8097000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8010700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8271100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8414000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8055500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7581000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8017000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7682900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6736900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6303800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6181800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5992700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6041700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6914200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7533400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7597400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6992500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5177900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5068500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4919100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4583800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4663000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4630300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4517800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4166000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4247900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4153300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3980000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3748900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3677800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3968500</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4325,8 +4429,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4403,112 +4507,118 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17373200</v>
+      </c>
+      <c r="E48" s="3">
         <v>17686600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>17489800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>17311200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>17186000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>16752700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>16379300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>16146700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15906300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15396800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14967400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14634200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>14439100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>14160500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13909300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>13614100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13373300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13045200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12675800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12280900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12074500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>11770500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>11425800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>11148800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2970800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2921900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2857300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2758400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2701300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2654900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2574800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2487300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2434500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2388500</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4549,7 +4659,7 @@
         <v>5538300</v>
       </c>
       <c r="P49" s="3">
-        <v>5538400</v>
+        <v>5538300</v>
       </c>
       <c r="Q49" s="3">
         <v>5538400</v>
@@ -4558,7 +4668,7 @@
         <v>5538400</v>
       </c>
       <c r="S49" s="3">
-        <v>5538500</v>
+        <v>5538400</v>
       </c>
       <c r="T49" s="3">
         <v>5538500</v>
@@ -4567,7 +4677,7 @@
         <v>5538500</v>
       </c>
       <c r="V49" s="3">
-        <v>5538600</v>
+        <v>5538500</v>
       </c>
       <c r="W49" s="3">
         <v>5538600</v>
@@ -4576,43 +4686,46 @@
         <v>5538600</v>
       </c>
       <c r="Y49" s="3">
+        <v>5538600</v>
+      </c>
+      <c r="Z49" s="3">
         <v>5538700</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>5538800</v>
       </c>
       <c r="AA49" s="3">
         <v>5538800</v>
       </c>
       <c r="AB49" s="3">
-        <v>5538900</v>
+        <v>5538800</v>
       </c>
       <c r="AC49" s="3">
         <v>5538900</v>
       </c>
       <c r="AD49" s="3">
-        <v>5539000</v>
+        <v>5538900</v>
       </c>
       <c r="AE49" s="3">
         <v>5539000</v>
       </c>
       <c r="AF49" s="3">
-        <v>5539100</v>
+        <v>5539000</v>
       </c>
       <c r="AG49" s="3">
         <v>5539100</v>
       </c>
       <c r="AH49" s="3">
-        <v>5539200</v>
+        <v>5539100</v>
       </c>
       <c r="AI49" s="3">
         <v>5539200</v>
       </c>
       <c r="AJ49" s="3">
+        <v>5539200</v>
+      </c>
+      <c r="AK49" s="3">
         <v>5539300</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4715,8 +4828,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4819,85 +4935,88 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E52" s="3">
         <v>59000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>61500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>63000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>60600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>62600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>64000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>63500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>57700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>55000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>50700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>46900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>46100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>44600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>47400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>42400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>36600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>36400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>35700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>36300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>34100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>35100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>33900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>33000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>31400</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>29900</v>
       </c>
       <c r="AC52" s="3">
         <v>29900</v>
@@ -4906,25 +5025,28 @@
         <v>29900</v>
       </c>
       <c r="AE52" s="3">
+        <v>29900</v>
+      </c>
+      <c r="AF52" s="3">
         <v>28800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>27400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>26900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>20900</v>
-      </c>
-      <c r="AI52" s="3">
-        <v>20800</v>
       </c>
       <c r="AJ52" s="3">
         <v>20800</v>
       </c>
+      <c r="AK52" s="3">
+        <v>20800</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5027,112 +5149,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>31132700</v>
+      </c>
+      <c r="E54" s="3">
         <v>31460400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>31813800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>31009500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>30795600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>30624600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>30395600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>29803900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>29083400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>29007200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>28239300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>26956300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>26327400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>25925300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>25487800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>25236700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>25862600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>26153400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>25847400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>24848300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>22825100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>22412800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>21917500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>21304300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>13204000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>13121000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>12943900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>12493200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>12516900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>12374800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12120800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>11796400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>11672300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>11917100</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5169,8 +5297,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5207,150 +5336,154 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3833100</v>
+      </c>
+      <c r="E57" s="3">
         <v>4045400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3869300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3472500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3587400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3651800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3681600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3679200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3553000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4127100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4358400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3906900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3738600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3532600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3370000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3294400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3614100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3770500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3400600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2954400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2860700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2844200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2727100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2452900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2385500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2336800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2295000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2018300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2009800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1978000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1880700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1622800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1557600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1948100</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1979600</v>
+      </c>
+      <c r="E58" s="3">
         <v>1964400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2194900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2176100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2155700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2105300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1331400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1561800</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M58" s="3">
-        <v>900600</v>
+      <c r="M58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N58" s="3">
         <v>900600</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>8</v>
+      <c r="O58" s="3">
+        <v>900600</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>8</v>
@@ -5370,8 +5503,8 @@
       <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V58" s="3">
-        <v>600</v>
+      <c r="V58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W58" s="3">
         <v>600</v>
@@ -5386,10 +5519,10 @@
         <v>600</v>
       </c>
       <c r="AA58" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB58" s="3">
         <v>2000</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>1900</v>
       </c>
       <c r="AC58" s="3">
         <v>1900</v>
@@ -5398,441 +5531,456 @@
         <v>1900</v>
       </c>
       <c r="AE58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AF58" s="3">
         <v>401300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>401500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>401400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>401200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>501000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>501500</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E59" s="3">
         <v>14500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>17200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>410000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2334800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2375600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2307800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2144400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2240800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2207900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2109100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2021000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2096700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2115700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2010500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1888300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1682300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1661300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1584600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1503300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>628400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>643500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>618600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>505100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>553800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>558200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>524700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>668100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>564300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>510100</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6868700</v>
+      </c>
+      <c r="E60" s="3">
         <v>7110700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7141200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6641900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6725700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6787100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6033900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6100700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5887800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6502600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7566800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6951800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5979400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5740500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5479100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5315400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5710800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5886200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5411200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4843200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4543000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4506000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4312300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3956700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3015900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2982200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2915500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2525300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2964900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2937800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2806800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2692000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2622800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2959700</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15483800</v>
+      </c>
+      <c r="E61" s="3">
         <v>15601800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>16019100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15945700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>15935000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>15981400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16704400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>16428600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7009400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5985700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4290700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3947500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4172100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4127400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4156800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4130700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4131000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4131600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4089000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3967200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2912000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2762500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2573500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2732100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2862700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2902400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2776800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2862500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2604600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2719600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2683100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2632100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2710600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2673200</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>262800</v>
+      </c>
+      <c r="E62" s="3">
         <v>267300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>254400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>264100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>251900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>252100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>240400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>228000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10644400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10425000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10193300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10095400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9914000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9867600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9714800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>9540700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>9359600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>9150100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8991200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8828400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8667600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8496000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8282600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8042800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>908000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>880500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>872700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>869100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>821600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>973200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>943900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>943300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>932600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>922300</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5935,8 +6083,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6039,8 +6190,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6143,112 +6297,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>23719000</v>
+      </c>
+      <c r="E66" s="3">
         <v>24117800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>24553500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24009300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24046500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>24172700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>24097900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>23868700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>23541600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>22913400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>22050800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20994700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>20065400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19735500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>19350700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>18986800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19201400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>19167900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>18491400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>17638900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>16122600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>15764500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>15168400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>14731600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6786600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6765100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6565000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6256900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6391100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6630600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6433700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6267500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6266000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6555200</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6285,8 +6445,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6389,8 +6550,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6493,8 +6657,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6597,8 +6764,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6701,112 +6871,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3405700</v>
+      </c>
+      <c r="E72" s="3">
         <v>3344200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3277400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3033000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2799400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2527200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2380500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2041100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1656100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2222800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2364100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2157600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2474000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2461200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2429800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2588000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3006100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3346800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3759000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3659800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3162700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3120700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3234900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3074600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2941100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2890100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2928100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2795600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2698400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2334500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2286100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2136400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2015900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1978000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6909,8 +7085,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7013,8 +7192,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7117,112 +7299,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7413700</v>
+      </c>
+      <c r="E76" s="3">
         <v>7342600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7260200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7000200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6749100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6451900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6297700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5935300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5541800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6093800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6188500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5961600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6262000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6189800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6137100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6249900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6661200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6985500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7356100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7209500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6702500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6648300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6749200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6572700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6417400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6355900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6378900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6236300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6125800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5744200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5687100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5528900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5406300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5361900</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7325,221 +7513,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
         <v>45597</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45506</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45415</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45324</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45233</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45142</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45051</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44960</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44862</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44771</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44680</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44589</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44498</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44407</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44316</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44225</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44134</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44043</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43952</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43861</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43770</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43679</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43588</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43497</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43406</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43315</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43224</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43133</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43042</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42951</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42860</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42769</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>191200</v>
+      </c>
+      <c r="E81" s="3">
         <v>196500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>374200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>363300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>401800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>276200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>468800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>514400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>659100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>526200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>678000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>552700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>597400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>487000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>637000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>677700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>642700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>574300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>787600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>650400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>535400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>365600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>426600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>385000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>483200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>334100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>407200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>364900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>712200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>252500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>294800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>279500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>414200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7576,112 +7773,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>223000</v>
+      </c>
+      <c r="E83" s="3">
         <v>215500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>208400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>201900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>192400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>182800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>177200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>172600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>192400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>182800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>177200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>172600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>166400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>162300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>158500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>154100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>149800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>145800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>141000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>137700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>132400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>126500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>123400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>122500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>117800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>114900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>112200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>109300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>105700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>101000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>99000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>98600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>97500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>95400</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7784,8 +7985,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7888,8 +8092,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7992,8 +8199,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8096,8 +8306,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8200,112 +8413,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>800900</v>
+      </c>
+      <c r="E89" s="3">
         <v>542400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>988900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>663800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>949800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>715300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>535600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>191100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>736400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>300200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>498500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>449500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>639100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>909200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>614600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>703000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>492600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>476200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1171000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1736300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>576900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>530600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>556300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>574200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>629400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>416800</v>
-      </c>
-      <c r="AC89" s="3">
-        <v>548600</v>
       </c>
       <c r="AD89" s="3">
         <v>548600</v>
       </c>
       <c r="AE89" s="3">
+        <v>548600</v>
+      </c>
+      <c r="AF89" s="3">
         <v>659200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>356700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>275800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>510500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>480600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>331100</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8342,112 +8561,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-272800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-341400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-353700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-342000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-459700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-472600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-404800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-363100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-482400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-419400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-377200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-281600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-291100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-260900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-240700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-277700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-330400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-273400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-228700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-195400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-266800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-225000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-148300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-144800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-183500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-179900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-206300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-164600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-157800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-174600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-170500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-143500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-154400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-138100</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8550,8 +8773,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8654,112 +8880,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-271400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-340800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-353000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-341200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-458500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-470800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-403100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-361600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-479500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-419200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-375800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-280800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-290100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-258800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-239700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-276900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-328900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-272900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-228100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-195000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-266300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-224500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-147300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-144300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-182500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-179500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-205600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-164000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-157400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-173900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-170300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-143400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-149400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-136200</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8796,112 +9028,116 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>129700</v>
+      </c>
+      <c r="E96" s="3">
         <v>129800</v>
-      </c>
-      <c r="E96" s="3">
-        <v>129700</v>
       </c>
       <c r="F96" s="3">
         <v>129700</v>
       </c>
       <c r="G96" s="3">
+        <v>129700</v>
+      </c>
+      <c r="H96" s="3">
         <v>129600</v>
-      </c>
-      <c r="H96" s="3">
-        <v>129500</v>
       </c>
       <c r="I96" s="3">
         <v>129500</v>
       </c>
       <c r="J96" s="3">
+        <v>129500</v>
+      </c>
+      <c r="K96" s="3">
         <v>129400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-121300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-123000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-124200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-125300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-96800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-97300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-98300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-99800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-87300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-88400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-89700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-90600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-80800</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-81600</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-82400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-82800</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-75300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>118300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-271900</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-77700</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-70000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-70600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-71000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-71300</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-68900</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-70100</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9004,8 +9240,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9108,8 +9347,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9212,112 +9454,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-134200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-887100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-133900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-139200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-319500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-232000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-92600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>102000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-238000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>155500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-132100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-177900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-492800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-475400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-749200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1114600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-986600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-963500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-657200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>892200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-346300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-289500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-420600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-394300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-472100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-242000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-361700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-368100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-460600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-170700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-97300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-349000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-343600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-179700</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9342,8 +9590,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9420,108 +9668,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>395300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-685400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>502000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>183400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>171800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>40000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-68500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>18800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>36500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-9400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-9200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-143800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>175000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-374400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-688500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-822900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-760200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>285700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2433600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-35800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>16500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-11500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>35600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-25200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-18700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>16500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>41200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>12000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>8200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>18100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-12300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>15200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
   <si>
     <t>DG</t>
   </si>
@@ -1361,8 +1361,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>226700</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1612,7 +1612,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>10010300</v>
+        <v>9783600</v>
       </c>
       <c r="E17" s="3">
         <v>9859600</v>
@@ -1719,7 +1719,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>294200</v>
+        <v>520900</v>
       </c>
       <c r="E18" s="3">
         <v>323800</v>
@@ -1972,7 +1972,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>547800</v>
+        <v>774500</v>
       </c>
       <c r="E21" s="3">
         <v>570800</v>
@@ -5557,7 +5557,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>10100</v>
+        <v>409000</v>
       </c>
       <c r="E59" s="3">
         <v>14500</v>

--- a/AAII_Financials/Quarterly/DG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
   <si>
     <t>DG</t>
   </si>
@@ -656,455 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45779</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45597</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45506</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45415</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45324</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45233</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45142</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45051</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44960</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44862</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44771</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44680</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44589</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44498</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44407</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44316</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44225</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44134</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44043</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43952</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43861</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43770</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43679</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43588</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43497</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43406</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43315</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43224</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43133</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43042</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42951</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42860</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42769</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10436000</v>
+      </c>
+      <c r="E8" s="3">
         <v>10304500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10183400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10210400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9914000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9858500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9694100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9796200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9342800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10202900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9464900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9425700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8751400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8651400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8517800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8650200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8401000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8414500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8199600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8684200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8448400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7157600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6991400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6981800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6623200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6649800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6417500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6443300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6114500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6129400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5903600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5828300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5609600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>6009200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5320000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7204700</v>
+      </c>
+      <c r="E9" s="3">
         <v>7274900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7247100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7150900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6921900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6952200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6881600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6751500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6387400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7054600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6579700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6377500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6013000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5951200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5898400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5912500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5645300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5677800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5631400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5866000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5852800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4884900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4926300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4832800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4620900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4578100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4522400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4468400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4252200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4164000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4137200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4037800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3910600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4108500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3732500</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3231300</v>
+      </c>
+      <c r="E10" s="3">
         <v>3029600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2936300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3059500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2992100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2906300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2812500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3044700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2955500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3148300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2885200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3048200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2738400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2700200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2619400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2737700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2755700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2736700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2568200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2818200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2595600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2272700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2065100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2149000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2002300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2071700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1895100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1974900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1862300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1965400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1766500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1790500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1699000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1900700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1587500</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1142,8 +1154,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1249,8 +1262,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1356,37 +1372,40 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>226700</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>6700</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1409,8 +1428,8 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1421,18 +1440,18 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>31000</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1445,8 +1464,8 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
@@ -1454,8 +1473,8 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
+      <c r="AI14" s="3">
+        <v>0</v>
       </c>
       <c r="AJ14" s="3" t="s">
         <v>8</v>
@@ -1463,38 +1482,41 @@
       <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>252800</v>
+      </c>
+      <c r="E15" s="3">
         <v>253600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>247000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>238800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>232300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>223000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>215500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>208400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>201900</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1570,8 +1592,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1606,222 +1631,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9859900</v>
+      </c>
+      <c r="E17" s="3">
         <v>9783600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9859600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9660400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9367900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9272200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9260600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9103900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8602000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9269700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8729300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8512300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8005200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7854800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7852300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7800600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7492100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7542300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7426500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7641600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7581700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6436800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6500000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6404000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6110900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6011300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5975300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5897800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5624300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5506000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5486200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5335200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5135800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5328600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>4927000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>576100</v>
+      </c>
+      <c r="E18" s="3">
         <v>520900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>323800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>550000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>546100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>586400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>433500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>692300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>740900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>933200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>735600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>913400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>746200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>796600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>665500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>849600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>908900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>872200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>773100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1042600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>866700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>720800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>491400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>577800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>512300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>638500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>442200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>545500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>490200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>623400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>417400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>493100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>473800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>680600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>393000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1859,8 +1891,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1888,15 +1921,15 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-400</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1943,11 +1976,11 @@
         <v>0</v>
       </c>
       <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
@@ -1958,444 +1991,459 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ20" s="3">
-        <v>0</v>
-      </c>
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>828900</v>
+      </c>
+      <c r="E21" s="3">
         <v>774500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>570800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>788800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>778400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>809300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>649000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>900700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>942800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1125500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>917900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1090600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>918700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>963000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>827900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1008100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1063000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1022000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>919000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1183600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1004400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>853300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>617900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>701200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>634700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>756300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>557000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>656600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>599500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>729100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>518400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>592200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>568900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>778200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>488400</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>64600</v>
+      </c>
+      <c r="E22" s="3">
         <v>65900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>67800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>68100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>72400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>77100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>82300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>84300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>83000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>74800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>53700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>43100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>39700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>38500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>39200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>39400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>40400</v>
-      </c>
-      <c r="T22" s="3">
-        <v>40300</v>
       </c>
       <c r="U22" s="3">
         <v>40300</v>
       </c>
       <c r="V22" s="3">
+        <v>40300</v>
+      </c>
+      <c r="W22" s="3">
         <v>39300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>30500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>25600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>24300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>24800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>25900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>25100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>24600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>25500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>24800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>24300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>24000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>23700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>25000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>25500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>511500</v>
+      </c>
+      <c r="E23" s="3">
         <v>228300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>256000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>481800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>473700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>502500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>351200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>608000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>657800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>858400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>681400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>870300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>706500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>758200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>626400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>810100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>868500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>832000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>732800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1003300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>836300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>695300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>467200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>553000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>486300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>613400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>417600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>519000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>465400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>599200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>393400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>469400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>445300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>655100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>369100</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>119600</v>
+      </c>
+      <c r="E24" s="3">
         <v>37100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>59400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>107600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>110400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>74900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>139100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>143400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>199200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>155300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>192300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>153800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>160700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>139400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>173100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>190700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>189200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>158600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>215700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>185800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>159900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>101600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>126400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>101300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>142400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>83400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>111800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>100600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>197800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>140900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>174600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>165800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>240900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2501,222 +2549,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>391900</v>
+      </c>
+      <c r="E26" s="3">
         <v>191200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>196500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>374200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>363300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>401800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>276200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>468800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>514400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>659100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>526200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>678000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>552700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>597400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>487000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>637000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>677700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>642700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>574300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>787600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>650400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>535400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>365600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>426600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>385000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>471000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>334100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>407200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>364900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>401400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>252500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>294800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>279500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>414200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>391900</v>
+      </c>
+      <c r="E27" s="3">
         <v>191200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>196500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>374200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>363300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>401800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>276200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>468800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>514400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>659100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>526200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>678000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>552700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>597400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>487000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>637000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>677700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>642700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>574300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>787600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>650400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>535400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>365600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>426600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>385000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>471000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>334100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>407200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>364900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>401400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>252500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>294800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>279500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>414200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2822,8 +2879,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2878,8 +2938,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2887,11 +2947,11 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2899,24 +2959,24 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>12200</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>310800</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2929,8 +2989,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3036,8 +3099,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3143,8 +3209,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3172,15 +3241,15 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>400</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -3227,11 +3296,11 @@
         <v>0</v>
       </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>1000</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
@@ -3242,123 +3311,129 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ32" s="3">
-        <v>0</v>
-      </c>
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>391900</v>
+      </c>
+      <c r="E33" s="3">
         <v>191200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>196500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>374200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>363300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>401800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>276200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>468800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>514400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>659100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>526200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>678000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>552700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>597400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>487000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>637000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>677700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>642700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>574300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>787600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>650400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>535400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>365600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>426600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>385000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>483200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>334100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>407200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>364900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>712200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>252500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>294800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>279500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>414200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3464,227 +3539,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>391900</v>
+      </c>
+      <c r="E35" s="3">
         <v>191200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>196500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>374200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>363300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>401800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>276200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>468800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>514400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>659100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>526200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>678000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>552700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>597400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>487000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>637000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>677700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>642700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>574300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>787600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>650400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>535400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>365600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>426600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>385000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>483200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>334100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>407200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>364900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>712200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>252500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>294800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>279500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>414200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45779</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45597</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45506</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45415</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45324</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45233</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45142</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45051</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44960</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44862</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44771</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44680</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44589</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44498</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44407</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44316</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44225</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44134</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44043</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43952</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43861</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43770</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43679</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43588</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43497</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43406</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43315</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43224</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43133</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43042</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42951</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42860</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42769</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3722,8 +3806,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3761,115 +3846,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>850000</v>
+      </c>
+      <c r="E41" s="3">
         <v>932600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>537300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1222700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>720700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>537300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>365400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>353000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>313100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>381600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>362700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>326300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>335600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>344800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>488700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>313700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>688100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1376600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2199400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2959600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2673900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>240300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>276100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>259600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>271100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>235500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>260700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>265300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>284000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>267400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>226200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>214200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>206000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>187900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>200200</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3975,222 +4064,231 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E43" s="3">
         <v>127100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>115700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>61500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>34900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>112300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>197600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>151700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>50900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>135800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>188100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>93300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>33600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>97400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>120400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>127000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>16600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>90800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>111100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>36200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>17200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>76500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>103200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>61700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>25200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>57800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>114600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>68400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>28600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>108300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>99700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>44300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>10500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>11100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>54600</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6590100</v>
+      </c>
+      <c r="E44" s="3">
         <v>6711200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7119000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7000600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6934400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6994300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7356100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7531500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7335800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6760700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7144700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6935900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6087400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5614300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5298900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5279300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5099500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5247500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5025800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4391200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4107300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4676800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4496400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4419600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4109800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4097000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3979100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3896400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3594500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3609000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3597200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3463000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3300100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>3258800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>3488200</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4218,193 +4316,199 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>302900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>321500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>327500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>280300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>247300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>273900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>272800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>237600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>199400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>197000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>210500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>194000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>184200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>192900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>178300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>177700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>272700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>275900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>287800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>258900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>263100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>230300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>258600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>232400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>220000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>225400</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7896300</v>
+      </c>
+      <c r="E46" s="3">
         <v>8163900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8176500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8724200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8097000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8010700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8271100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8414000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8055500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7581000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8017000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7682900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6736900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6303800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6181800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5992700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6041700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6914200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7533400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7597400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6992500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5177900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5068500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4919100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4583800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4663000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4630300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4517800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4166000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4247900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4153300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3980000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3748900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3677800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3968500</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4432,8 +4536,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4510,115 +4614,121 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17497800</v>
+      </c>
+      <c r="E48" s="3">
         <v>17373200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>17686600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>17489800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>17311200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>17186000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>16752700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>16379300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>16146700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15906300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>15396800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14967400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>14634200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>14439100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>14160500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>13909300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13614100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13373300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13045200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12675800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12280900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>12074500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>11770500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>11425800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11148800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2970800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2921900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2857300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2758400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2701300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2654900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2574800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2487300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2434500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2388500</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4662,7 +4772,7 @@
         <v>5538300</v>
       </c>
       <c r="Q49" s="3">
-        <v>5538400</v>
+        <v>5538300</v>
       </c>
       <c r="R49" s="3">
         <v>5538400</v>
@@ -4671,7 +4781,7 @@
         <v>5538400</v>
       </c>
       <c r="T49" s="3">
-        <v>5538500</v>
+        <v>5538400</v>
       </c>
       <c r="U49" s="3">
         <v>5538500</v>
@@ -4680,7 +4790,7 @@
         <v>5538500</v>
       </c>
       <c r="W49" s="3">
-        <v>5538600</v>
+        <v>5538500</v>
       </c>
       <c r="X49" s="3">
         <v>5538600</v>
@@ -4689,43 +4799,46 @@
         <v>5538600</v>
       </c>
       <c r="Z49" s="3">
+        <v>5538600</v>
+      </c>
+      <c r="AA49" s="3">
         <v>5538700</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>5538800</v>
       </c>
       <c r="AB49" s="3">
         <v>5538800</v>
       </c>
       <c r="AC49" s="3">
-        <v>5538900</v>
+        <v>5538800</v>
       </c>
       <c r="AD49" s="3">
         <v>5538900</v>
       </c>
       <c r="AE49" s="3">
-        <v>5539000</v>
+        <v>5538900</v>
       </c>
       <c r="AF49" s="3">
         <v>5539000</v>
       </c>
       <c r="AG49" s="3">
-        <v>5539100</v>
+        <v>5539000</v>
       </c>
       <c r="AH49" s="3">
         <v>5539100</v>
       </c>
       <c r="AI49" s="3">
-        <v>5539200</v>
+        <v>5539100</v>
       </c>
       <c r="AJ49" s="3">
         <v>5539200</v>
       </c>
       <c r="AK49" s="3">
+        <v>5539200</v>
+      </c>
+      <c r="AL49" s="3">
         <v>5539300</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4831,8 +4944,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4938,88 +5054,91 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>55300</v>
+      </c>
+      <c r="E52" s="3">
         <v>57300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>59000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>61500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>63000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>60600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>62600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>64000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>63500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>57700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>55000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>50700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>46900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>46100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>44600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>47400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>42400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>36600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>36400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>35700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>36300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>34100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>35100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>33900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>33000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>31400</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>29900</v>
       </c>
       <c r="AD52" s="3">
         <v>29900</v>
@@ -5028,25 +5147,28 @@
         <v>29900</v>
       </c>
       <c r="AF52" s="3">
+        <v>29900</v>
+      </c>
+      <c r="AG52" s="3">
         <v>28800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>27400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>26900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>20900</v>
-      </c>
-      <c r="AJ52" s="3">
-        <v>20800</v>
       </c>
       <c r="AK52" s="3">
         <v>20800</v>
       </c>
+      <c r="AL52" s="3">
+        <v>20800</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5152,115 +5274,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30987700</v>
+      </c>
+      <c r="E54" s="3">
         <v>31132700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>31460400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>31813800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>31009500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>30795600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>30624600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>30395600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>29803900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>29083400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>29007200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>28239300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>26956300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>26327400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>25925300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>25487800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>25236700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>25862600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>26153400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>25847400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>24848300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>22825100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>22412800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>21917500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>21304300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>13204000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>13121000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>12943900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>12493200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>12516900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12374800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>12120800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>11796400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>11672300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>11917100</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5298,8 +5426,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5337,156 +5466,160 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3836200</v>
+      </c>
+      <c r="E57" s="3">
         <v>3833100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4045400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3869300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3472500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3587400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3651800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3681600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3679200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3553000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4127100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4358400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3906900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3738600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3532600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3370000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3294400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3614100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3770500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3400600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2954400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2860700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2844200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2727100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2452900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2385500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2336800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2295000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2018300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2009800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1978000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1880700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1622800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1557600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1948100</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1498500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1979600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1964400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2194900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2176100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2155700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2105300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1331400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1561800</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N58" s="3">
-        <v>900600</v>
+      <c r="N58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O58" s="3">
         <v>900600</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>8</v>
+      <c r="P58" s="3">
+        <v>900600</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>8</v>
@@ -5506,8 +5639,8 @@
       <c r="V58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W58" s="3">
-        <v>600</v>
+      <c r="W58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X58" s="3">
         <v>600</v>
@@ -5522,10 +5655,10 @@
         <v>600</v>
       </c>
       <c r="AB58" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC58" s="3">
         <v>2000</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>1900</v>
       </c>
       <c r="AD58" s="3">
         <v>1900</v>
@@ -5534,453 +5667,468 @@
         <v>1900</v>
       </c>
       <c r="AF58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AG58" s="3">
         <v>401300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>401500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>401400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>401200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>501000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>501500</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E59" s="3">
         <v>409000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>14500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>17200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>410000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>16900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2334800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2375600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2307800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2144400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2240800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2207900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2109100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2021000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2096700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2115700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2010500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1888300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1682300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1661300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1584600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1503300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>628400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>643500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>618600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>505100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>553800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>558200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>524700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>668100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>564300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>510100</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6403700</v>
+      </c>
+      <c r="E60" s="3">
         <v>6868700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7110700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7141200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6641900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6725700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6787100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6033900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6100700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5887800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6502600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7566800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6951800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5979400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5740500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5479100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5315400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5710800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5886200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5411200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4843200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4543000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4506000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4312300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3956700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3015900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2982200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2915500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2525300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2964900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2937800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2806800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2692000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2622800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2959700</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15519500</v>
+      </c>
+      <c r="E61" s="3">
         <v>15483800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15601800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16019100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>15945700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>15935000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>15981400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>16704400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>16428600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7009400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5985700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4290700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3947500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4172100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4127400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4156800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4130700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4131000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4131600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4089000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3967200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2912000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2762500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2573500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2732100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2862700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2902400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2776800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2862500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2604600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2719600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2683100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2632100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2710600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2673200</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>264800</v>
+      </c>
+      <c r="E62" s="3">
         <v>262800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>267300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>254400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>264100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>251900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>252100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>240400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>228000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10644400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10425000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10193300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>10095400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9914000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9867600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>9714800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>9540700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>9359600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>9150100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8991200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8828400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8667600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8496000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8282600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8042800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>908000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>880500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>872700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>869100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>821600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>973200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>943900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>943300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>932600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>922300</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6086,8 +6234,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6193,8 +6344,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6300,115 +6454,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>23284000</v>
+      </c>
+      <c r="E66" s="3">
         <v>23719000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>24117800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24553500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24009300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>24046500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>24172700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>24097900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>23868700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>23541600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>22913400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>22050800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>20994700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>20065400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>19735500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19350700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>18986800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>19201400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>19167900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>18491400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>17638900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>16122600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>15764500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>15168400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>14731600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6786600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6765100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6565000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6256900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6391100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6630600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6433700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6267500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6266000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6555200</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6446,8 +6606,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6553,8 +6714,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6660,8 +6824,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6767,8 +6934,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6874,115 +7044,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3667800</v>
+      </c>
+      <c r="E72" s="3">
         <v>3405700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3344200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3277400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3033000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2799400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2527200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2380500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2041100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1656100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2222800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2364100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2157600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2474000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2461200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2429800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2588000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3006100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3346800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3759000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3659800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3162700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3120700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3234900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>3074600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2941100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2890100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2928100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2795600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2698400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2334500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2286100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2136400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2015900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1978000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7088,8 +7264,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7195,8 +7374,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7302,115 +7484,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7703700</v>
+      </c>
+      <c r="E76" s="3">
         <v>7413700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7342600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7260200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7000200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6749100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6451900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6297700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5935300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5541800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6093800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6188500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5961600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6262000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6189800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6137100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6249900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6661200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6985500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7356100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7209500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6702500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6648300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6749200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6572700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6417400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6355900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6378900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6236300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6125800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5744200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5687100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5528900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5406300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>5361900</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7516,227 +7704,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45779</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45597</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45506</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45415</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45324</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45233</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45142</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45051</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44960</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44862</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44771</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44680</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44589</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44498</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44407</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44316</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44225</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44134</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44043</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43952</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43861</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43770</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43679</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43588</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43497</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43406</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43315</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43224</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43133</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43042</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42951</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42860</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42769</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>391900</v>
+      </c>
+      <c r="E81" s="3">
         <v>191200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>196500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>374200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>363300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>401800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>276200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>468800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>514400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>659100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>526200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>678000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>552700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>597400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>487000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>637000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>677700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>642700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>574300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>787600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>650400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>535400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>365600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>426600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>385000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>483200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>334100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>407200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>364900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>712200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>252500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>294800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>279500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>414200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7774,115 +7971,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>232300</v>
+      </c>
+      <c r="E83" s="3">
         <v>223000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>215500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>208400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>201900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>192400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>182800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>177200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>172600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>192400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>182800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>177200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>172600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>166400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>162300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>158500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>154100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>149800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>145800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>141000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>137700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>132400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>126500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>123400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>122500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>117800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>114900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>112200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>109300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>105700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>101000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>99000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>98600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>97500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>95400</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7988,8 +8189,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8095,8 +8299,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8202,8 +8409,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8309,8 +8519,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8416,115 +8629,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>847200</v>
+      </c>
+      <c r="E89" s="3">
         <v>800900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>542400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>988900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>663800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>949800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>715300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>535600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>191100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>736400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>300200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>498500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>449500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>639100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>909200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>614600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>703000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>492600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>476200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1171000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1736300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>576900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>530600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>556300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>574200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>629400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>416800</v>
-      </c>
-      <c r="AD89" s="3">
-        <v>548600</v>
       </c>
       <c r="AE89" s="3">
         <v>548600</v>
       </c>
       <c r="AF89" s="3">
+        <v>548600</v>
+      </c>
+      <c r="AG89" s="3">
         <v>659200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>356700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>275800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>510500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>480600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>331100</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8562,115 +8781,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-290900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-272800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-341400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-353700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-342000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-459700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-472600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-404800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-363100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-482400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-419400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-377200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-281600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-291100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-260900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-240700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-277700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-330400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-273400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-228700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-195400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-266800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-225000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-148300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-144800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-183500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-179900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-206300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-164600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-157800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-174600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-170500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-143500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-154400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-138100</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8776,8 +8999,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8883,115 +9109,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-290400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-271400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-340800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-353000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-341200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-458500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-470800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-403100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-361600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-479500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-419200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-375800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-280800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-290100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-258800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-239700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-276900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-328900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-272900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-228100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-195000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-266300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-224500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-147300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-144300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-182500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-179500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-205600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-164000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-157400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-173900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-170300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-143400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-149400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-136200</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9029,115 +9261,119 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>129800</v>
+      </c>
+      <c r="E96" s="3">
         <v>129700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>129800</v>
-      </c>
-      <c r="F96" s="3">
-        <v>129700</v>
       </c>
       <c r="G96" s="3">
         <v>129700</v>
       </c>
       <c r="H96" s="3">
+        <v>129700</v>
+      </c>
+      <c r="I96" s="3">
         <v>129600</v>
-      </c>
-      <c r="I96" s="3">
-        <v>129500</v>
       </c>
       <c r="J96" s="3">
         <v>129500</v>
       </c>
       <c r="K96" s="3">
+        <v>129500</v>
+      </c>
+      <c r="L96" s="3">
         <v>129400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-121300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-123000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-124200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-125300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-96800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-97300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-98300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-99800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-87300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-88400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-89700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-90600</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-80800</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-81600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-82400</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-82800</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-75300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>118300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-271900</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-77700</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-70000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-70600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-71000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-71300</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-68900</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-70100</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9243,8 +9479,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9350,8 +9589,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9457,115 +9699,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-639300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-134200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-887100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-133900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-139200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-319500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-232000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-92600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>102000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-238000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>155500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-132100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-177900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-492800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-475400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-749200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1114600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-986600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-963500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-657200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>892200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-346300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-289500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-420600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-394300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-472100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-242000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-361700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-368100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-460600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-170700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-97300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-349000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-343600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-179700</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9593,8 +9841,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9671,111 +9919,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-82600</v>
+      </c>
+      <c r="E102" s="3">
         <v>395300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-685400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>502000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>183400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>171800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>12400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>40000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-68500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>18800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>36500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-9400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-9200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-143800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>175000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-374400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-688500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-822900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-760200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>285700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2433600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-35800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>16500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-11500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>35600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-25200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-18700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>16500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>41200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>12000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>8200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>18100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-12300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>15200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
   <si>
     <t>DG</t>
   </si>
@@ -656,479 +656,491 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45961</v>
+      </c>
+      <c r="E7" s="2">
         <v>45870</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45779</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45688</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45597</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45506</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45415</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45324</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45233</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45142</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45051</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44960</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44862</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44771</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44680</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44589</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44498</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44407</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44316</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44225</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44134</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44043</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43952</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43861</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43770</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43679</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43588</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43497</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43406</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43315</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43224</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43133</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43042</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42951</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42860</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42769</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10649500</v>
+      </c>
+      <c r="E8" s="3">
         <v>10727700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10436000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10304500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10183400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10210400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9914000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9858500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9694100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9796200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9342800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10202900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9464900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9425700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8751400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8651400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8517800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8650200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8401000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8414500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8199600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8684200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8448400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7157600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6991400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6981800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6623200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6649800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6417500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6443300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6114500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6129400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5903600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5828300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5609600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>6009200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>5320000</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7465100</v>
+      </c>
+      <c r="E9" s="3">
         <v>7366100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7204700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7274900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7247100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7150900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6921900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6952200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6881600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6751500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6387400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7054600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6579700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6377500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6013000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5951200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5898400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5912500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5645300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5677800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5631400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5866000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5852800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4884900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4926300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4832800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4620900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4578100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4522400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4468400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4252200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4164000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4137200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4037800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3910600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>4108500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>3732500</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3184300</v>
+      </c>
+      <c r="E10" s="3">
         <v>3361700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3231300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3029600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2936300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3059500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2992100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2906300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2812500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3044700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2955500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3148300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2885200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3048200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2738400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2700200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2619400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2737700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2755700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2736700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2568200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2818200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2595600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2272700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2065100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2149000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2002300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2071700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1895100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1974900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1862300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1965400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1766500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1790500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1699000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1900700</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1587500</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1168,8 +1180,9 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1281,8 +1294,11 @@
       <c r="AM12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1394,8 +1410,11 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1405,32 +1424,32 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>226700</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>6700</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1453,8 +1472,8 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1465,18 +1484,18 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>31000</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1489,8 +1508,8 @@
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI14" s="3">
         <v>0</v>
@@ -1498,8 +1517,8 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
-      <c r="AK14" s="3" t="s">
-        <v>8</v>
+      <c r="AK14" s="3">
+        <v>0</v>
       </c>
       <c r="AL14" s="3" t="s">
         <v>8</v>
@@ -1507,44 +1526,47 @@
       <c r="AM14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>266300</v>
+      </c>
+      <c r="E15" s="3">
         <v>256800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>252800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>253600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>247000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>238800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>232300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>223000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>215500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>208400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>201900</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
@@ -1620,8 +1642,11 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1658,234 +1683,241 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10223600</v>
+      </c>
+      <c r="E17" s="3">
         <v>10132300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9859900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9783600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9859600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9660400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9367900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9272200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9260600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9103900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8602000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9269700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8729300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8512300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8005200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7854800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7852300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7800600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7492100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7542300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7426500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7641600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7581700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6436800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6500000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6404000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6110900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6011300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5975300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5897800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5624300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5506000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5486200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5335200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5135800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>5328600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>4927000</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>425900</v>
+      </c>
+      <c r="E18" s="3">
         <v>595400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>576100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>520900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>323800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>550000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>546100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>586400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>433500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>692300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>740900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>933200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>735600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>913400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>746200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>796600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>665500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>849600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>908900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>872200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>773100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1042600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>866700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>720800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>491400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>577800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>512300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>638500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>442200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>545500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>490200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>623400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>417400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>493100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>473800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>680600</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>393000</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1925,8 +1957,9 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1960,15 +1993,15 @@
       <c r="M20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
+      <c r="N20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-400</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -2015,11 +2048,11 @@
         <v>0</v>
       </c>
       <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
       <c r="AH20" s="3">
         <v>0</v>
       </c>
@@ -2030,468 +2063,483 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AL20" s="3">
-        <v>0</v>
-      </c>
       <c r="AM20" s="3">
         <v>0</v>
       </c>
+      <c r="AN20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>692200</v>
+      </c>
+      <c r="E21" s="3">
         <v>852200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>828900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>774500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>570800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>788800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>778400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>809300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>649000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>900700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>942800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1125500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>917900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1090600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>918700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>963000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>827900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1008100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1063000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1022000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>919000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1183600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1004400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>853300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>617900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>701200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>634700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>756300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>557000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>656600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>599500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>729100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>518400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>592200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>568900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>778200</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>488400</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>55900</v>
+      </c>
+      <c r="E22" s="3">
         <v>57700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>64600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>65900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>67800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>68100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>72400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>77100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>82300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>84300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>83000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>74800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>53700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>43100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>39700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>38500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>39200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>39400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>40400</v>
-      </c>
-      <c r="V22" s="3">
-        <v>40300</v>
       </c>
       <c r="W22" s="3">
         <v>40300</v>
       </c>
       <c r="X22" s="3">
+        <v>40300</v>
+      </c>
+      <c r="Y22" s="3">
         <v>39300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>30500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>25600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>24300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>24800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>25900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>25100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>24600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>25500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>24800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>24300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>24000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>23700</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>25000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>25500</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>369900</v>
+      </c>
+      <c r="E23" s="3">
         <v>537700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>511500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>228300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>256000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>481800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>473700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>502500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>351200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>608000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>657800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>858400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>681400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>870300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>706500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>758200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>626400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>810100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>868500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>832000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>732800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1003300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>836300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>695300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>467200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>553000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>486300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>613400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>417600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>519000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>465400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>599200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>393400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>469400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>445300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>655100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>369100</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>87300</v>
+      </c>
+      <c r="E24" s="3">
         <v>126300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>119600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>37100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>59400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>107600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>110400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>74900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>139100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>143400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>199200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>155300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>192300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>153800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>160700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>139400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>173100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>190700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>189200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>158600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>215700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>185800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>159900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>101600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>126400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>101300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>142400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>83400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>111800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>100600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>197800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>140900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>174600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>165800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>240900</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2603,234 +2651,243 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>282700</v>
+      </c>
+      <c r="E26" s="3">
         <v>411400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>391900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>191200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>196500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>374200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>363300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>401800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>276200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>468800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>514400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>659100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>526200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>678000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>552700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>597400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>487000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>637000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>677700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>642700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>574300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>787600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>650400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>535400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>365600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>426600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>385000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>471000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>334100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>407200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>364900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>401400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>252500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>294800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>279500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>414200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>282700</v>
+      </c>
+      <c r="E27" s="3">
         <v>411400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>391900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>191200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>196500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>374200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>363300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>401800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>276200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>468800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>514400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>659100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>526200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>678000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>552700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>597400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>487000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>637000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>677700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>642700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>574300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>787600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>650400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>535400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>365600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>426600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>385000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>471000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>334100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>407200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>364900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>401400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>252500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>294800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>279500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>414200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2942,8 +2999,11 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3004,8 +3064,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -3013,11 +3073,11 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3025,24 +3085,24 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>12200</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI29" s="3">
         <v>310800</v>
       </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3055,8 +3115,11 @@
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3168,8 +3231,11 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3281,8 +3347,11 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3316,15 +3385,15 @@
       <c r="M32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
+      <c r="N32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>400</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -3371,11 +3440,11 @@
         <v>0</v>
       </c>
       <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>1000</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
       <c r="AH32" s="3">
         <v>0</v>
       </c>
@@ -3386,129 +3455,135 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="3">
         <v>3500</v>
       </c>
-      <c r="AL32" s="3">
-        <v>0</v>
-      </c>
       <c r="AM32" s="3">
         <v>0</v>
       </c>
+      <c r="AN32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>282700</v>
+      </c>
+      <c r="E33" s="3">
         <v>411400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>391900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>191200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>196500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>374200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>363300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>401800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>276200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>468800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>514400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>659100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>526200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>678000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>552700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>597400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>487000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>637000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>677700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>642700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>574300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>787600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>650400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>535400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>365600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>426600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>385000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>483200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>334100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>407200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>364900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>712200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>252500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>294800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>279500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>414200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3620,239 +3695,248 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>282700</v>
+      </c>
+      <c r="E35" s="3">
         <v>411400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>391900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>191200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>196500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>374200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>363300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>401800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>276200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>468800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>514400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>659100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>526200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>678000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>552700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>597400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>487000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>637000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>677700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>642700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>574300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>787600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>650400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>535400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>365600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>426600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>385000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>483200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>334100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>407200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>364900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>712200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>252500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>294800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>279500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>414200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45961</v>
+      </c>
+      <c r="E38" s="2">
         <v>45870</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45779</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45688</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45597</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45506</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45415</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45324</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45233</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45142</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45051</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44960</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44862</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44771</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44680</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44589</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44498</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44407</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44316</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44225</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44134</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44043</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43952</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43861</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43770</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43679</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43588</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43497</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43406</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43315</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43224</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43133</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43042</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42951</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42860</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42769</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3892,8 +3976,9 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3933,121 +4018,125 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1240600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1284600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>850000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>932600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>537300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1222700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>720700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>537300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>365400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>353000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>313100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>381600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>362700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>326300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>335600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>344800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>488700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>313700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>688100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1376600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2199400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2959600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2673900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>240300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>276100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>259600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>271100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>235500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>260700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>265300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>284000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>267400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>226200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>214200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>206000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>187900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>200200</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4159,234 +4248,243 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>65400</v>
+      </c>
+      <c r="E43" s="3">
         <v>81700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>31900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>127100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>115700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>61500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>34900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>112300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>197600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>151700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>50900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>135800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>188100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>93300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>33600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>97400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>120400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>127000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>16600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>90800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>111100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>36200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>17200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>76500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>103200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>61700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>25200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>57800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>114600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>68400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>28600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>108300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>99700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>44300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>10500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>11100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>54600</v>
       </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6653900</v>
+      </c>
+      <c r="E44" s="3">
         <v>6609700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6590100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6711200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7119000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7000600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6934400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6994300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7356100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7531500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7335800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6760700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7144700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6935900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6087400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5614300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5298900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5279300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5099500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5247500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5025800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4391200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4107300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4676800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4496400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4419600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4109800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4097000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3979100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3896400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3594500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3609000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3597200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>3463000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>3300100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>3258800</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>3488200</v>
       </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4420,199 +4518,205 @@
       <c r="M45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O45" s="3">
         <v>302900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>321500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>327500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>280300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>247300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>273900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>272800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>237600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>199400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>197000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>210500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>194000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>184200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>192900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>178300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>177700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>272700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>275900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>287800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>258900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>263100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>230300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>258600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>232400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>220000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>225400</v>
       </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8379100</v>
+      </c>
+      <c r="E46" s="3">
         <v>8398700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7896300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8163900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8176500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8724200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8097000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8010700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8271100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8414000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8055500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7581000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8017000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7682900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6736900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6303800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6181800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5992700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6041700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6914200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7533400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7597400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6992500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5177900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5068500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4919100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4583800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4663000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4630300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4517800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4166000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4247900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4153300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3980000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3748900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>3677800</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>3968500</v>
       </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4646,8 +4750,8 @@
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -4724,121 +4828,127 @@
       <c r="AM47" s="3">
         <v>0</v>
       </c>
+      <c r="AN47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17746100</v>
+      </c>
+      <c r="E48" s="3">
         <v>17660300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>17497800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>17373200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>17686600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>17489800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>17311200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>17186000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>16752700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16379300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>16146700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15906300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15396800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>14967400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>14634200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>14439100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>14160500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13909300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13614100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13373300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13045200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>12675800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>12280900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>12074500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11770500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11425800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11148800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2970800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2921900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2857300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2758400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2701300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2654900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2574800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2487300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2434500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2388500</v>
       </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4888,7 +4998,7 @@
         <v>5538300</v>
       </c>
       <c r="S49" s="3">
-        <v>5538400</v>
+        <v>5538300</v>
       </c>
       <c r="T49" s="3">
         <v>5538400</v>
@@ -4897,7 +5007,7 @@
         <v>5538400</v>
       </c>
       <c r="V49" s="3">
-        <v>5538500</v>
+        <v>5538400</v>
       </c>
       <c r="W49" s="3">
         <v>5538500</v>
@@ -4906,7 +5016,7 @@
         <v>5538500</v>
       </c>
       <c r="Y49" s="3">
-        <v>5538600</v>
+        <v>5538500</v>
       </c>
       <c r="Z49" s="3">
         <v>5538600</v>
@@ -4915,43 +5025,46 @@
         <v>5538600</v>
       </c>
       <c r="AB49" s="3">
+        <v>5538600</v>
+      </c>
+      <c r="AC49" s="3">
         <v>5538700</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>5538800</v>
       </c>
       <c r="AD49" s="3">
         <v>5538800</v>
       </c>
       <c r="AE49" s="3">
-        <v>5538900</v>
+        <v>5538800</v>
       </c>
       <c r="AF49" s="3">
         <v>5538900</v>
       </c>
       <c r="AG49" s="3">
-        <v>5539000</v>
+        <v>5538900</v>
       </c>
       <c r="AH49" s="3">
         <v>5539000</v>
       </c>
       <c r="AI49" s="3">
-        <v>5539100</v>
+        <v>5539000</v>
       </c>
       <c r="AJ49" s="3">
         <v>5539100</v>
       </c>
       <c r="AK49" s="3">
-        <v>5539200</v>
+        <v>5539100</v>
       </c>
       <c r="AL49" s="3">
         <v>5539200</v>
       </c>
       <c r="AM49" s="3">
+        <v>5539200</v>
+      </c>
+      <c r="AN49" s="3">
         <v>5539300</v>
       </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5063,8 +5176,11 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5176,94 +5292,97 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>55100</v>
+      </c>
+      <c r="E52" s="3">
         <v>55800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>55300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>57300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>59000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>61500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>63000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>60600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>62600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>64000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>63500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>57700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>55000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>50700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>46900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>46100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>44600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>47400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>42400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>36600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>36400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>35700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>36300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>34100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>35100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>33900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>33000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>31400</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>29900</v>
       </c>
       <c r="AF52" s="3">
         <v>29900</v>
@@ -5272,25 +5391,28 @@
         <v>29900</v>
       </c>
       <c r="AH52" s="3">
+        <v>29900</v>
+      </c>
+      <c r="AI52" s="3">
         <v>28800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>27400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>26900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>20900</v>
-      </c>
-      <c r="AL52" s="3">
-        <v>20800</v>
       </c>
       <c r="AM52" s="3">
         <v>20800</v>
       </c>
+      <c r="AN52" s="3">
+        <v>20800</v>
+      </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5402,121 +5524,127 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>31718600</v>
+      </c>
+      <c r="E54" s="3">
         <v>31653100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>30987700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>31132700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>31460400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>31813800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>31009500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>30795600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>30624600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>30395600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>29803900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>29083400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>29007200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>28239300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>26956300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>26327400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>25925300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>25487800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>25236700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>25862600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>26153400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>25847400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>24848300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>22825100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>22412800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>21917500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>21304300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>13204000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>13121000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>12943900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12493200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>12516900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>12374800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>12120800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>11796400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>11672300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>11917100</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5556,8 +5684,9 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5597,168 +5726,172 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4295400</v>
+      </c>
+      <c r="E57" s="3">
         <v>3970600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3836200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3833100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4045400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3869300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3472500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3587400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3651800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3681600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3679200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3553000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4127100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4358400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3906900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3738600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3532600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3370000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3294400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3614100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3770500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3400600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2954400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2860700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2844200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2727100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2452900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2385500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2336800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2295000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2018300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2009800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1978000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1880700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1622800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1557600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1948100</v>
       </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1539900</v>
+      </c>
+      <c r="E58" s="3">
         <v>1521900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1498500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1979600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1964400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2194900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2176100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2155700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2105300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1331400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1561800</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P58" s="3">
-        <v>900600</v>
+      <c r="P58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q58" s="3">
         <v>900600</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>8</v>
+      <c r="R58" s="3">
+        <v>900600</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>8</v>
@@ -5778,8 +5911,8 @@
       <c r="X58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y58" s="3">
-        <v>600</v>
+      <c r="Y58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z58" s="3">
         <v>600</v>
@@ -5794,10 +5927,10 @@
         <v>600</v>
       </c>
       <c r="AD58" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE58" s="3">
         <v>2000</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>1900</v>
       </c>
       <c r="AF58" s="3">
         <v>1900</v>
@@ -5806,477 +5939,492 @@
         <v>1900</v>
       </c>
       <c r="AH58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AI58" s="3">
         <v>401300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>401500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>401400</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>401200</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>501000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>501500</v>
       </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E59" s="3">
         <v>11300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>37700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>409000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>410000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2334800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2375600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2307800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2144400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2240800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2207900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2109100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2021000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2096700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2115700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2010500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1888300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1682300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1661300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1584600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1503300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>628400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>643500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>618600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>505100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>553800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>558200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>524700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>668100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>564300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>510100</v>
       </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7153000</v>
+      </c>
+      <c r="E60" s="3">
         <v>6701700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6403700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6868700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7110700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7141200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6641900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6725700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6787100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6033900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6100700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5887800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6502600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7566800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6951800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5979400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5740500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5479100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5315400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5710800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5886200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5411200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4843200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4543000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4506000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4312300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3956700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3015900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2982200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2915500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2525300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2964900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2937800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2806800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2692000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2622800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2959700</v>
       </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14968500</v>
+      </c>
+      <c r="E61" s="3">
         <v>15546000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15519500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15483800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>15601800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>16019100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>15945700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>15935000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>15981400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>16704400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>16428600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7009400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5985700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4290700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3947500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4172100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4127400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4156800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4130700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4131000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4131600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4089000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3967200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2912000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2762500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2573500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2732100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2862700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2902400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2776800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2862500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2604600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2719600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2683100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2632100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2710600</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2673200</v>
       </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>277000</v>
+      </c>
+      <c r="E62" s="3">
         <v>265500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>264800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>262800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>267300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>254400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>264100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>251900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>252100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>240400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>228000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10644400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>10425000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>10193300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>10095400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>9914000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>9867600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>9714800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>9540700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>9359600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>9150100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8991200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8828400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8667600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8496000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8282600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8042800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>908000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>880500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>872700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>869100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>821600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>973200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>943900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>943300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>932600</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>922300</v>
       </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6388,8 +6536,11 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6501,8 +6652,11 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6614,121 +6768,127 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>23532400</v>
+      </c>
+      <c r="E66" s="3">
         <v>23641000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>23284000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>23719000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24117800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>24553500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>24009300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>24046500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>24172700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>24097900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>23868700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>23541600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>22913400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>22050800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>20994700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>20065400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19735500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>19350700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>18986800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19201400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19167900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>18491400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>17638900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>16122600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>15764500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>15168400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>14731600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6786600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6765100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6565000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6256900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6391100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6630600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6433700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6267500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>6266000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>6555200</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6768,8 +6928,9 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6881,8 +7042,11 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6994,8 +7158,11 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7107,8 +7274,11 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7220,121 +7390,127 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4102100</v>
+      </c>
+      <c r="E72" s="3">
         <v>3949300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3667800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3405700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3344200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3277400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3033000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2799400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2527200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2380500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2041100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1656100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2222800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2364100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2157600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2474000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2461200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2429800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2588000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3006100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3346800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3759000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3659800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3162700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>3120700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>3234900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>3074600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2941100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2890100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2928100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2795600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2698400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2334500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2286100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>2136400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>2015900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1978000</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7446,8 +7622,11 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7559,8 +7738,11 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7672,121 +7854,127 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8186100</v>
+      </c>
+      <c r="E76" s="3">
         <v>8012100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7703700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7413700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7342600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7260200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7000200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6749100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6451900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6297700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5935300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5541800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6093800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6188500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5961600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6262000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6189800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6137100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6249900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6661200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6985500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7356100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7209500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6702500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6648300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6749200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6572700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6417400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6355900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6378900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6236300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6125800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5744200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5687100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>5528900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>5406300</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>5361900</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7898,239 +8086,248 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45961</v>
+      </c>
+      <c r="E80" s="2">
         <v>45870</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45779</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45688</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45597</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45506</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45415</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45324</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45233</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45142</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45051</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44960</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44862</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44771</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44680</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44589</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44498</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44407</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44316</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44225</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44134</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44043</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43952</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43861</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43770</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43679</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43588</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43497</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43406</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43315</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43224</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43133</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43042</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42951</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42860</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42769</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>282700</v>
+      </c>
+      <c r="E81" s="3">
         <v>411400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>391900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>191200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>196500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>374200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>363300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>401800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>276200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>468800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>514400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>659100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>526200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>678000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>552700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>597400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>487000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>637000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>677700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>642700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>574300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>787600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>650400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>535400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>365600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>426600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>385000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>483200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>334100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>407200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>364900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>712200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>252500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>294800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>279500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>414200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8170,121 +8367,125 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>247000</v>
+      </c>
+      <c r="E83" s="3">
         <v>238800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>232300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>223000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>215500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>208400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>201900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>192400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>182800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>177200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>172600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>192400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>182800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>177200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>172600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>166400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>162300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>158500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>154100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>149800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>145800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>141000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>137700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>132400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>126500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>123400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>122500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>117800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>114900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>112200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>109300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>105700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>101000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>99000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>98600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>97500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>95400</v>
       </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8396,8 +8597,11 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8509,8 +8713,11 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8622,8 +8829,11 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8735,8 +8945,11 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8848,121 +9061,127 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1004000</v>
+      </c>
+      <c r="E89" s="3">
         <v>967700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>847200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>800900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>542400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>988900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>663800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>949800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>715300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>535600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>191100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>736400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>300200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>498500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>449500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>639100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>909200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>614600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>703000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>492600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>476200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1171000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1736300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>576900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>530600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>556300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>574200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>629400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>416800</v>
-      </c>
-      <c r="AF89" s="3">
-        <v>548600</v>
       </c>
       <c r="AG89" s="3">
         <v>548600</v>
       </c>
       <c r="AH89" s="3">
+        <v>548600</v>
+      </c>
+      <c r="AI89" s="3">
         <v>659200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>356700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>275800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>510500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>480600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>331100</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9002,121 +9221,125 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-313500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-403000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-290900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-272800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-341400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-353700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-342000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-459700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-472600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-404800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-363100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-482400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-419400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-377200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-281600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-291100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-260900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-240700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-277700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-330400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-273400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-228700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-195400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-266800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-225000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-148300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-144800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-183500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-179900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-206300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-164600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-157800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-174600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-170500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-143500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-154400</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-138100</v>
       </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9228,8 +9451,11 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9341,121 +9567,127 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-312700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-401100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-290400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-271400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-340800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-353000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-341200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-458500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-470800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-403100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-361600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-479500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-419200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-375800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-280800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-290100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-258800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-239700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-276900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-328900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-272900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-228100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-195000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-266300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-224500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-147300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-144300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-182500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-179500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-205600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-164000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-157400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-173900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-170300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-143400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-149400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-136200</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9495,8 +9727,9 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9504,112 +9737,115 @@
         <v>129900</v>
       </c>
       <c r="E96" s="3">
+        <v>129900</v>
+      </c>
+      <c r="F96" s="3">
         <v>129800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>129700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>129800</v>
-      </c>
-      <c r="H96" s="3">
-        <v>129700</v>
       </c>
       <c r="I96" s="3">
         <v>129700</v>
       </c>
       <c r="J96" s="3">
+        <v>129700</v>
+      </c>
+      <c r="K96" s="3">
         <v>129600</v>
-      </c>
-      <c r="K96" s="3">
-        <v>129500</v>
       </c>
       <c r="L96" s="3">
         <v>129500</v>
       </c>
       <c r="M96" s="3">
+        <v>129500</v>
+      </c>
+      <c r="N96" s="3">
         <v>129400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-121300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-123000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-124200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-125300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-96800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-97300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-98300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-99800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-87300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-88400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-89700</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-90600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-80800</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-81600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-82400</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-82800</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-75300</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>118300</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-271900</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-77700</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-70000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-70600</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-71000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-71300</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-68900</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-70100</v>
       </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9721,8 +9957,11 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9834,8 +10073,11 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9947,121 +10189,127 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-735200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-132000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-639300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-134200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-887100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-133900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-139200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-319500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-232000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-92600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>102000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-238000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>155500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-132100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-177900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-492800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-475400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-749200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1114600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-986600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-963500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-657200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>892200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-346300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-289500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-420600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-394300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-472100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-242000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-361700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-368100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-460600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-170700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-97300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-349000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-343600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-179700</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10095,8 +10343,8 @@
       <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -10173,117 +10421,123 @@
       <c r="AM101" s="3">
         <v>0</v>
       </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="E102" s="3">
         <v>434500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-82600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>395300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-685400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>502000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>183400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>171800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>12400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>40000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-68500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>18800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>36500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-9200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-143800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>175000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-374400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-688500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-822900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-760200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>285700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2433600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-35800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>16500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-11500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>35600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-25200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-4600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-18700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>16500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>41200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>12000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>8200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>18100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-12300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>15200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="92">
   <si>
     <t>DG</t>
   </si>
@@ -656,491 +656,503 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46052</v>
+      </c>
+      <c r="E7" s="2">
         <v>45961</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45870</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45779</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45688</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45597</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45506</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45415</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45324</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45233</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45142</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45051</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44960</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44862</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44771</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44680</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44589</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44498</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44407</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44316</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44225</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44134</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44043</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43952</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43861</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43770</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43679</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43588</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43497</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43406</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43315</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43224</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43133</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43042</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42951</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42860</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42769</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10911200</v>
+      </c>
+      <c r="E8" s="3">
         <v>10649500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10727700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10436000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10304500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10183400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10210400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9914000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9858500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9694100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9796200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9342800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10202900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9464900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9425700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8751400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8651400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8517800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8650200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8401000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8414500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8199600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8684200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8448400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7157600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6991400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6981800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6623200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6649800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6417500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6443300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6114500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6129400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5903600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5828300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>5609600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>6009200</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>5320000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7588800</v>
+      </c>
+      <c r="E9" s="3">
         <v>7465100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7366100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7204700</v>
       </c>
-      <c r="G9" s="3">
-        <v>7274900</v>
-      </c>
       <c r="H9" s="3">
+        <v>7257000</v>
+      </c>
+      <c r="I9" s="3">
         <v>7247100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7150900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6921900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6952200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6881600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6751500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6387400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7054600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6579700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6377500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6013000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5951200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5898400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5912500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5645300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5677800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5631400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5866000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5852800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4884900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4926300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4832800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4620900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4578100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4522400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4468400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4252200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4164000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4137200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4037800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>3910600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>4108500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>3732500</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3322400</v>
+      </c>
+      <c r="E10" s="3">
         <v>3184300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3361700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3231300</v>
       </c>
-      <c r="G10" s="3">
-        <v>3029600</v>
-      </c>
       <c r="H10" s="3">
+        <v>3047500</v>
+      </c>
+      <c r="I10" s="3">
         <v>2936300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3059500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2992100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2906300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2812500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3044700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2955500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3148300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2885200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3048200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2738400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2700200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2619400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2737700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2755700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2736700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2568200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2818200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2595600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2272700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2065100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2149000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2002300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2071700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1895100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1974900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1862300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1965400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1766500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1790500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1699000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1900700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1587500</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1181,8 +1193,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1297,8 +1310,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1413,13 +1429,16 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>65600</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1427,11 +1446,11 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>226700</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
+        <v>244600</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -1439,20 +1458,20 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>6700</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1475,8 +1494,8 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
@@ -1487,18 +1506,18 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>31000</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1511,8 +1530,8 @@
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ14" s="3">
         <v>0</v>
@@ -1520,8 +1539,8 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
-      <c r="AL14" s="3" t="s">
-        <v>8</v>
+      <c r="AL14" s="3">
+        <v>0</v>
       </c>
       <c r="AM14" s="3" t="s">
         <v>8</v>
@@ -1529,47 +1548,50 @@
       <c r="AN14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>270400</v>
+      </c>
+      <c r="E15" s="3">
         <v>266300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>256800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>252800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>253600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>247000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>238800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>232300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>223000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>215500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>208400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>201900</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1645,8 +1667,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,240 +1709,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10247800</v>
+      </c>
+      <c r="E17" s="3">
         <v>10223600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10132300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9859900</v>
       </c>
-      <c r="G17" s="3">
-        <v>9783600</v>
-      </c>
       <c r="H17" s="3">
+        <v>9765700</v>
+      </c>
+      <c r="I17" s="3">
         <v>9859600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9660400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9367900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9272200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9260600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9103900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8602000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9269700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8729300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8512300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8005200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7854800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7852300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7800600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7492100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7542300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7426500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7641600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7581700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6436800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6500000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6404000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6110900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6011300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5975300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5897800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5624300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5506000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5486200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5335200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>5135800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>5328600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>4927000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>663400</v>
+      </c>
+      <c r="E18" s="3">
         <v>425900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>595400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>576100</v>
       </c>
-      <c r="G18" s="3">
-        <v>520900</v>
-      </c>
       <c r="H18" s="3">
+        <v>538800</v>
+      </c>
+      <c r="I18" s="3">
         <v>323800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>550000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>546100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>586400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>433500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>692300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>740900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>933200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>735600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>913400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>746200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>796600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>665500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>849600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>908900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>872200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>773100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1042600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>866700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>720800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>491400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>577800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>512300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>638500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>442200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>545500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>490200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>623400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>417400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>493100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>473800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>680600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>393000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1958,8 +1990,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1996,15 +2029,15 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-400</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -2051,11 +2084,11 @@
         <v>0</v>
       </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
       <c r="AI20" s="3">
         <v>0</v>
       </c>
@@ -2066,480 +2099,495 @@
         <v>0</v>
       </c>
       <c r="AL20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AM20" s="3">
-        <v>0</v>
-      </c>
       <c r="AN20" s="3">
         <v>0</v>
       </c>
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>933700</v>
+      </c>
+      <c r="E21" s="3">
         <v>692200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>852200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>828900</v>
       </c>
-      <c r="G21" s="3">
-        <v>774500</v>
-      </c>
       <c r="H21" s="3">
+        <v>792400</v>
+      </c>
+      <c r="I21" s="3">
         <v>570800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>788800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>778400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>809300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>649000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>900700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>942800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1125500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>917900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1090600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>918700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>963000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>827900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1008100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1063000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1022000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>919000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1183600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1004400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>853300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>617900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>701200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>634700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>756300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>557000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>656600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>599500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>729100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>518400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>592200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>568900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>778200</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>488400</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E22" s="3">
         <v>55900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>57700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>64600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>65900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>67800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>68100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>72400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>77100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>82300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>84300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>83000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>74800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>53700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>43100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>39700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>38500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>39200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>39400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>40400</v>
-      </c>
-      <c r="W22" s="3">
-        <v>40300</v>
       </c>
       <c r="X22" s="3">
         <v>40300</v>
       </c>
       <c r="Y22" s="3">
+        <v>40300</v>
+      </c>
+      <c r="Z22" s="3">
         <v>39300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>30500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>25600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>24300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>24800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>25900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>25100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>24600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>25500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>24800</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>24300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>24000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>23700</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>25000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>25500</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>545500</v>
+      </c>
+      <c r="E23" s="3">
         <v>369900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>537700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>511500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>228300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>256000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>481800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>473700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>502500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>351200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>608000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>657800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>858400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>681400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>870300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>706500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>758200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>626400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>810100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>868500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>832000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>732800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1003300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>836300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>695300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>467200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>553000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>486300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>613400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>417600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>519000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>465400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>599200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>393400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>469400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>445300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>655100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>369100</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>119200</v>
+      </c>
+      <c r="E24" s="3">
         <v>87300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>126300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>119600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>37100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>59400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>107600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>110400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>74900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>139100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>143400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>199200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>155300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>192300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>153800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>160700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>139400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>173100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>190700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>189200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>158600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>215700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>185800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>159900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>101600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>126400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>101300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>142400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>83400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>111800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>100600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>197800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>140900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>174600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>165800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>240900</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2654,240 +2702,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>426300</v>
+      </c>
+      <c r="E26" s="3">
         <v>282700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>411400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>391900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>191200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>196500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>374200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>363300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>401800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>276200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>468800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>514400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>659100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>526200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>678000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>552700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>597400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>487000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>637000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>677700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>642700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>574300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>787600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>650400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>535400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>365600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>426600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>385000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>471000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>334100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>407200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>364900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>401400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>252500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>294800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>279500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>414200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>426300</v>
+      </c>
+      <c r="E27" s="3">
         <v>282700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>411400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>391900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>191200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>196500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>374200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>363300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>401800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>276200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>468800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>514400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>659100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>526200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>678000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>552700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>597400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>487000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>637000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>677700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>642700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>574300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>787600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>650400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>535400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>365600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>426600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>385000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>471000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>334100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>407200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>364900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>401400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>252500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>294800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>279500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>414200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3002,8 +3059,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3067,8 +3127,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -3076,11 +3136,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -3088,24 +3148,24 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>12200</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>310800</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3118,8 +3178,11 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3234,8 +3297,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3350,8 +3416,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3388,15 +3457,15 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>400</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -3443,11 +3512,11 @@
         <v>0</v>
       </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>1000</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
       <c r="AI32" s="3">
         <v>0</v>
       </c>
@@ -3458,132 +3527,138 @@
         <v>0</v>
       </c>
       <c r="AL32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="3">
         <v>3500</v>
       </c>
-      <c r="AM32" s="3">
-        <v>0</v>
-      </c>
       <c r="AN32" s="3">
         <v>0</v>
       </c>
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>426300</v>
+      </c>
+      <c r="E33" s="3">
         <v>282700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>411400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>391900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>191200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>196500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>374200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>363300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>401800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>276200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>468800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>514400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>659100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>526200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>678000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>552700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>597400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>487000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>637000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>677700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>642700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>574300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>787600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>650400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>535400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>365600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>426600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>385000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>483200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>334100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>407200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>364900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>712200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>252500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>294800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>279500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>414200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3698,245 +3773,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>426300</v>
+      </c>
+      <c r="E35" s="3">
         <v>282700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>411400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>391900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>191200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>196500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>374200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>363300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>401800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>276200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>468800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>514400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>659100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>526200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>678000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>552700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>597400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>487000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>637000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>677700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>642700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>574300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>787600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>650400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>535400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>365600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>426600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>385000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>483200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>334100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>407200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>364900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>712200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>252500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>294800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>279500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>414200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46052</v>
+      </c>
+      <c r="E38" s="2">
         <v>45961</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45870</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45779</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45688</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45597</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45506</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45415</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45324</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45233</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45142</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45051</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44960</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44862</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44771</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44680</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44589</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44498</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44407</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44316</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44225</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44134</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44043</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43952</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43861</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43770</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43679</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43588</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43497</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43406</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43315</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43224</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43133</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43042</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42951</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42860</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42769</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3977,8 +4061,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4019,124 +4104,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1138500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1240600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1284600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>850000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>932600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>537300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1222700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>720700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>537300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>365400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>353000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>313100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>381600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>362700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>326300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>335600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>344800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>488700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>313700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>688100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1376600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2199400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2959600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2673900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>240300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>276100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>259600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>271100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>235500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>260700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>265300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>284000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>267400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>226200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>214200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>206000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>187900</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>200200</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4251,240 +4340,249 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E43" s="3">
         <v>65400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>81700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>31900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>127100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>115700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>61500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>34900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>112300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>197600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>151700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>50900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>135800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>188100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>93300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>33600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>97400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>120400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>127000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>16600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>90800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>111100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>36200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>17200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>76500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>103200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>61700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>25200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>57800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>114600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>68400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>28600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>108300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>99700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>44300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>10500</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>11100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>54600</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6331900</v>
+      </c>
+      <c r="E44" s="3">
         <v>6653900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6609700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6590100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6711200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7119000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7000600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6934400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6994300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7356100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7531500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7335800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6760700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7144700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6935900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>6087400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5614300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5298900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5279300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5099500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5247500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5025800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4391200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4107300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4676800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4496400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4419600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4109800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4097000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3979100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3896400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3594500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3609000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>3597200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>3463000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>3300100</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>3258800</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>3488200</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4521,202 +4619,208 @@
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
         <v>302900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>321500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>327500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>280300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>247300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>273900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>272800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>237600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>199400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>197000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>210500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>194000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>184200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>192900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>178300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>177700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>272700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>275900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>287800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>258900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>263100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>230300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>258600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>232400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>220000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>225400</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7897800</v>
+      </c>
+      <c r="E46" s="3">
         <v>8379100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8398700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7896300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8163900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8176500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8724200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8097000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8010700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8271100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8414000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8055500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7581000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8017000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7682900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6736900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6303800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6181800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5992700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6041700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6914200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7533400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7597400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6992500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5177900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5068500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4919100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4583800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4663000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4630300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4517800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4166000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4247900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4153300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3980000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>3748900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>3677800</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>3968500</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4753,8 +4857,8 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4831,129 +4935,135 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17471100</v>
+      </c>
+      <c r="E48" s="3">
         <v>17746100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>17660300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>17497800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>17373200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>17686600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>17489800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>17311200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>17186000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16752700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>16379300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>16146700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15906300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>15396800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>14967400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>14634200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>14439100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>14160500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13909300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13614100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13373300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13045200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>12675800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>12280900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>12074500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11770500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11425800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>11148800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2970800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2921900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2857300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2758400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2701300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2654900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2574800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2487300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2434500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2388500</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5538300</v>
+        <v>5538600</v>
       </c>
       <c r="E49" s="3">
         <v>5538300</v>
@@ -5001,7 +5111,7 @@
         <v>5538300</v>
       </c>
       <c r="T49" s="3">
-        <v>5538400</v>
+        <v>5538300</v>
       </c>
       <c r="U49" s="3">
         <v>5538400</v>
@@ -5010,7 +5120,7 @@
         <v>5538400</v>
       </c>
       <c r="W49" s="3">
-        <v>5538500</v>
+        <v>5538400</v>
       </c>
       <c r="X49" s="3">
         <v>5538500</v>
@@ -5019,7 +5129,7 @@
         <v>5538500</v>
       </c>
       <c r="Z49" s="3">
-        <v>5538600</v>
+        <v>5538500</v>
       </c>
       <c r="AA49" s="3">
         <v>5538600</v>
@@ -5028,43 +5138,46 @@
         <v>5538600</v>
       </c>
       <c r="AC49" s="3">
+        <v>5538600</v>
+      </c>
+      <c r="AD49" s="3">
         <v>5538700</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>5538800</v>
       </c>
       <c r="AE49" s="3">
         <v>5538800</v>
       </c>
       <c r="AF49" s="3">
-        <v>5538900</v>
+        <v>5538800</v>
       </c>
       <c r="AG49" s="3">
         <v>5538900</v>
       </c>
       <c r="AH49" s="3">
-        <v>5539000</v>
+        <v>5538900</v>
       </c>
       <c r="AI49" s="3">
         <v>5539000</v>
       </c>
       <c r="AJ49" s="3">
-        <v>5539100</v>
+        <v>5539000</v>
       </c>
       <c r="AK49" s="3">
         <v>5539100</v>
       </c>
       <c r="AL49" s="3">
-        <v>5539200</v>
+        <v>5539100</v>
       </c>
       <c r="AM49" s="3">
         <v>5539200</v>
       </c>
       <c r="AN49" s="3">
+        <v>5539200</v>
+      </c>
+      <c r="AO49" s="3">
         <v>5539300</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5179,8 +5292,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5295,97 +5411,100 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E52" s="3">
         <v>55100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>55800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>55300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>57300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>59000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>61500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>63000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>60600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>62600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>64000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>63500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>57700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>55000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>50700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>46900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>46100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>44600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>47400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>42400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>36600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>36400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>35700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>36300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>34100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>35100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>33900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>33000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>31400</v>
-      </c>
-      <c r="AF52" s="3">
-        <v>29900</v>
       </c>
       <c r="AG52" s="3">
         <v>29900</v>
@@ -5394,25 +5513,28 @@
         <v>29900</v>
       </c>
       <c r="AI52" s="3">
+        <v>29900</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>28800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>27400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>26900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>20900</v>
-      </c>
-      <c r="AM52" s="3">
-        <v>20800</v>
       </c>
       <c r="AN52" s="3">
         <v>20800</v>
       </c>
+      <c r="AO52" s="3">
+        <v>20800</v>
+      </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5527,124 +5649,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30963700</v>
+      </c>
+      <c r="E54" s="3">
         <v>31718600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>31653100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>30987700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>31132700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>31460400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>31813800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>31009500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>30795600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>30624600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>30395600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>29803900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>29083400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>29007200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>28239300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>26956300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>26327400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>25925300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>25487800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>25236700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>25862600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>26153400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>25847400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>24848300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>22825100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>22412800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>21917500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>21304300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>13204000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>13121000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12943900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>12493200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>12516900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>12374800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>12120800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>11796400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>11672300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>11917100</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5685,8 +5813,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5727,174 +5856,178 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4051600</v>
+      </c>
+      <c r="E57" s="3">
         <v>4295400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3970600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3836200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3833100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4045400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3869300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3472500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3587400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3651800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3681600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3679200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3553000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4127100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4358400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3906900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3738600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3532600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3370000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3294400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3614100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3770500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3400600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2954400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2860700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2844200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2727100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2452900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2385500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2336800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2295000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2018300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2009800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1978000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1880700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1622800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1557600</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1948100</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1546900</v>
+      </c>
+      <c r="E58" s="3">
         <v>1539900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1521900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1498500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1979600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1964400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2194900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2176100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2155700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2105300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1331400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1561800</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q58" s="3">
-        <v>900600</v>
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R58" s="3">
         <v>900600</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>8</v>
+      <c r="S58" s="3">
+        <v>900600</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>8</v>
@@ -5914,8 +6047,8 @@
       <c r="Y58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z58" s="3">
-        <v>600</v>
+      <c r="Z58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA58" s="3">
         <v>600</v>
@@ -5930,10 +6063,10 @@
         <v>600</v>
       </c>
       <c r="AE58" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF58" s="3">
         <v>2000</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>1900</v>
       </c>
       <c r="AG58" s="3">
         <v>1900</v>
@@ -5942,489 +6075,504 @@
         <v>1900</v>
       </c>
       <c r="AI58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>401300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>401500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>401400</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>401200</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>501000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>501500</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>554300</v>
+      </c>
+      <c r="E59" s="3">
         <v>11200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>37700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>409000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>14500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>17200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>410000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>16900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2334800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2375600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2307800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2144400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2240800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2207900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2109100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2021000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2096700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2115700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2010500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1888300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1682300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1661300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1584600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1503300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>628400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>643500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>618600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>505100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>553800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>558200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>524700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>668100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>564300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>510100</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6961100</v>
+      </c>
+      <c r="E60" s="3">
         <v>7153000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6701700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6403700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6868700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7110700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7141200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6641900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6725700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6787100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6033900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6100700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5887800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6502600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7566800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6951800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5979400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5740500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5479100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5315400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5710800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5886200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5411200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4843200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4543000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4506000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4312300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3956700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3015900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2982200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2915500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2525300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2964900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2937800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2806800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2692000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2622800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2959700</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14171800</v>
+      </c>
+      <c r="E61" s="3">
         <v>14968500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15546000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15519500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>15483800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>15601800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16019100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>15945700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>15935000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>15981400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>16704400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>16428600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7009400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5985700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4290700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3947500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4172100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4127400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4156800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4130700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4131000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4131600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4089000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3967200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2912000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2762500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2573500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2732100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2862700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2902400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2776800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2862500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2604600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2719600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2683100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2632100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2710600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2673200</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>280000</v>
+      </c>
+      <c r="E62" s="3">
         <v>277000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>265500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>264800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>262800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>267300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>254400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>264100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>251900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>252100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>240400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>228000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>10644400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>10425000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>10193300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>10095400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>9914000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>9867600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>9714800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>9540700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>9359600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>9150100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8991200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8828400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8667600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8496000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8282600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>8042800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>908000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>880500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>872700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>869100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>821600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>973200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>943900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>943300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>932600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>922300</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6539,8 +6687,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6655,8 +6806,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6771,124 +6925,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>22451800</v>
+      </c>
+      <c r="E66" s="3">
         <v>23532400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>23641000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>23284000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>23719000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>24117800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>24553500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>24009300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>24046500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>24172700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>24097900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>23868700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23541600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>22913400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>22050800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>20994700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>20065400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>19735500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>19350700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>18986800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19201400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>19167900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>18491400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>17638900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>16122600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>15764500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>15168400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>14731600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6786600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6765100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6565000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6256900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6391100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6630600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6433700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>6267500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>6266000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>6555200</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6929,8 +7089,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7045,8 +7206,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7161,8 +7325,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7277,8 +7444,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7393,124 +7563,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4398500</v>
+      </c>
+      <c r="E72" s="3">
         <v>4102100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3949300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3667800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3405700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3344200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3277400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3033000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2799400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2527200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2380500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2041100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1656100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2222800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2364100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2157600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2474000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2461200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2429800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2588000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3006100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3346800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3759000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3659800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>3162700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>3120700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>3234900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>3074600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2941100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2890100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2928100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2795600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2698400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2334500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>2286100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>2136400</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>2015900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1978000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7625,8 +7801,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7741,8 +7920,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7857,124 +8039,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8512000</v>
+      </c>
+      <c r="E76" s="3">
         <v>8186100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8012100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7703700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7413700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7342600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7260200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7000200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6749100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6451900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6297700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5935300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5541800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6093800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6188500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5961600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6262000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6189800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6137100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6249900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6661200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6985500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7356100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7209500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6702500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6648300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6749200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6572700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6417400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6355900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6378900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6236300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6125800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5744200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>5687100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>5528900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>5406300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>5361900</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8089,245 +8277,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46052</v>
+      </c>
+      <c r="E80" s="2">
         <v>45961</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45870</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45779</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45688</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45597</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45506</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45415</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45324</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45233</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45142</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45051</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44960</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44862</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44771</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44680</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44589</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44498</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44407</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44316</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44225</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44134</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44043</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43952</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43861</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43770</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43679</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43588</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43497</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43406</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43315</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43224</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43133</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43042</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42951</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42860</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42769</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>426300</v>
+      </c>
+      <c r="E81" s="3">
         <v>282700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>411400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>391900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>191200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>196500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>374200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>363300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>401800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>276200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>468800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>514400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>659100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>526200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>678000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>552700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>597400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>487000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>637000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>677700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>642700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>574300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>787600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>650400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>535400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>365600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>426600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>385000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>483200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>334100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>407200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>364900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>712200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>252500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>294800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>279500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>414200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>235300</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8368,124 +8565,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>253600</v>
+      </c>
+      <c r="E83" s="3">
         <v>247000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>238800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>232300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>223000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>215500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>208400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>201900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>192400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>182800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>177200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>172600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>192400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>182800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>177200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>172600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>166400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>162300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>158500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>154100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>149800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>145800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>141000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>137700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>132400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>126500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>123400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>122500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>117800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>114900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>112200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>109300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>105700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>101000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>99000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>98600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>97500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>95400</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8600,8 +8801,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8716,8 +8920,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8832,8 +9039,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8948,8 +9158,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9064,124 +9277,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>815700</v>
+      </c>
+      <c r="E89" s="3">
         <v>1004000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>967700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>847200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>800900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>542400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>988900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>663800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>949800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>715300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>535600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>191100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>736400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>300200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>498500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>449500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>639100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>909200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>614600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>703000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>492600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>476200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1171000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1736300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>576900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>530600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>556300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>574200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>629400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>416800</v>
-      </c>
-      <c r="AG89" s="3">
-        <v>548600</v>
       </c>
       <c r="AH89" s="3">
         <v>548600</v>
       </c>
       <c r="AI89" s="3">
+        <v>548600</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>659200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>356700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>275800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>510500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>480600</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>331100</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9222,124 +9441,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-233700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-313500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-403000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-290900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-272800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-341400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-353700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-342000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-459700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-472600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-404800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-363100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-482400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-419400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-377200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-281600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-291100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-260900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-240700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-277700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-330400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-273400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-228700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-195400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-266800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-225000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-148300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-144800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-183500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-179900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-206300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-164600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-157800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-174600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-170500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-143500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-154400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-138100</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9454,8 +9677,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9570,124 +9796,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-233000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-312700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-401100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-290400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-271400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-340800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-353000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-341200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-458500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-470800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-403100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-361600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-479500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-419200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-375800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-280800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-290100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-258800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-239700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-276900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-328900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-272900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-228100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-195000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-266300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-224500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-147300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-144300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-182500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-179500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-205600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-164000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-157400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-173900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-170300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-143400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-149400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-136200</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9728,8 +9960,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9740,112 +9973,115 @@
         <v>129900</v>
       </c>
       <c r="F96" s="3">
+        <v>129900</v>
+      </c>
+      <c r="G96" s="3">
         <v>129800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>129700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>129800</v>
-      </c>
-      <c r="I96" s="3">
-        <v>129700</v>
       </c>
       <c r="J96" s="3">
         <v>129700</v>
       </c>
       <c r="K96" s="3">
+        <v>129700</v>
+      </c>
+      <c r="L96" s="3">
         <v>129600</v>
-      </c>
-      <c r="L96" s="3">
-        <v>129500</v>
       </c>
       <c r="M96" s="3">
         <v>129500</v>
       </c>
       <c r="N96" s="3">
+        <v>129500</v>
+      </c>
+      <c r="O96" s="3">
         <v>129400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-121300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-123000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-124200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-125300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-96800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-97300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-98300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-99800</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-87300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-88400</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-89700</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-90600</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-80800</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-81600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-82400</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-82800</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-75300</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>118300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-271900</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-77700</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-70000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-70600</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-71000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-71300</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-68900</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-70100</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9960,8 +10196,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10076,8 +10315,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10192,124 +10434,130 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-684800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-735200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-132000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-639300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-134200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-887100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-133900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-139200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-319500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-232000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-92600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>102000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-238000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>155500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-132100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-177900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-492800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-475400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-749200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1114600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-986600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-963500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-657200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>892200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-346300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-289500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-420600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-394300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-472100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-242000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-361700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-368100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-460600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-170700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-97300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-349000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-343600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-179700</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10346,8 +10594,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10424,120 +10672,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-102100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-43900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>434500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-82600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>395300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-685400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>502000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>183400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>171800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>12400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>40000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-68500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>18800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>36500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-9400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-9200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-143800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>175000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-374400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-688500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-822900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-760200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>285700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2433600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-35800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>16500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-11500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>35600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-25200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-4600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-18700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>16500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>41200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>12000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>8200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>18100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-12300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>15200</v>
       </c>
     </row>
